--- a/Versionen/brettspiel-sept-final/game_data.xlsx
+++ b/Versionen/brettspiel-sept-final/game_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\_Privat\Coding\KlimSta\Versionen\brettspiel-sept-final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schneids\code\KlimSta-Brettspiel\Versionen\brettspiel-sept-final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED365E5E-0E90-4536-9D19-DB97225A467F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639654F2-8CF8-4295-8415-EE4B69F6CA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Massnahmenkarten Spielwerte" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,9 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0" xr:uid="{884F3275-8B47-4A24-9A63-26455AFB7D59}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     KgCO2/m²a</t>
       </text>
     </comment>
@@ -92,18 +92,18 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{EF592111-A8C2-4853-9B03-5FD652A65E13}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t xml:space="preserve">[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     €/m²
 </t>
       </text>
     </comment>
     <comment ref="H2" authorId="1" shapeId="0" xr:uid="{42E090DF-C6E0-4ACF-94D0-539FD66BF793}">
       <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
+        <t>[Kommentarthread]
+Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
+Kommentar:
     Geld token</t>
       </text>
     </comment>
@@ -112,7 +112,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="589">
   <si>
     <t>Name</t>
   </si>
@@ -223,9 +223,6 @@
   </si>
   <si>
     <t>*Flexibilität</t>
-  </si>
-  <si>
-    <t>E-Car Lade-Infrastruktur</t>
   </si>
   <si>
     <t>Biomasse-Kessel</t>
@@ -1164,9 +1161,6 @@
     <t>Benötigt eine elektrische Batterie</t>
   </si>
   <si>
-    <t>E-Car Wallboxen</t>
-  </si>
-  <si>
     <t>E-car wall boxes</t>
   </si>
   <si>
@@ -1327,9 +1321,6 @@
   </si>
   <si>
     <t>"Eine dezentrale Luftwärmepumpe ist vergleichsweise günstig und kann einzelne Wohnungen oder Bereiche direkt versorgen. Sie nutzt Außenluft als Wärmequelle, ist aber weniger effizient und kann durch Außengeräte, Lärm oder Platzbedarf im städtischen Umfeld problematisch sein."</t>
-  </si>
-  <si>
-    <t>"Eine Grundwasser-Wärmepumpe nutzt die relativ konstante Temperatur des Grundwassers und kann sehr effizient heizen und kühlen. Sie spart viele Emissionen, ist aber teuer, genehmigungspflichtig und nur bei geeigneten Standortbedingungen möglich."</t>
   </si>
   <si>
     <t>"Infrarotpaneele können in fast jedem Haus nachgerüstet werden, sind aber weit weniger effizient als Wärmepumpen und benötigen teuren Strom."</t>
@@ -1626,9 +1617,6 @@
     <t>"Eine Abwasser-Wärmepumpe nutzt Wärme aus dem Abwasserkanal, die sonst ungenutzt verloren gehen würde. Sie kann sehr effizient sein und viele Emissionen sparen, ist aber eine technisch anspruchsvolle und meist teurere Lösung."</t>
   </si>
   <si>
-    <t>di</t>
-  </si>
-  <si>
     <t>"Batteriespeicher werden immer günstiger. Sie können den eigenen PV-Strom in  den Abend retten und vermeiden so CO2-intensiveren  Stromnetzbezug."</t>
   </si>
   <si>
@@ -1848,40 +1836,49 @@
     <t>"Central air source heat pump"</t>
   </si>
   <si>
-    <t>"Bedingung: Keine Fassadenbegrünung"</t>
-  </si>
-  <si>
-    <t>"Bedingung: Wärmepumpe installiert"</t>
-  </si>
-  <si>
-    <t>"Voraussetzung: Private Wallboxen oder Hausweiter E-Car Port."</t>
-  </si>
-  <si>
-    <t>"Effekt: Speicher kann jetzt vom Netz beladen werden. Bei der Wertung des Speichers wird die Stromproduktionsbedingung ignoriert."</t>
-  </si>
-  <si>
-    <t>"Bedingung: Kein Kleiner Heimspeicher installiert"</t>
-  </si>
-  <si>
-    <t>"Bedingung: Kein Großer Batteriespeicher installiert"</t>
-  </si>
-  <si>
-    <t>"Bedingung: Keine Fassadenintegrierte PV installiert"</t>
-  </si>
-  <si>
-    <t>"Nicht kombinierbar mit Private Wallboxen. Ermöglicht Bi-Direktionelles Laden"</t>
-  </si>
-  <si>
     <t>"Nicht kombinierbar mit Hausweiter E-Car Port. Ermöglicht Bi-Direktionelles Laden"</t>
   </si>
   <si>
-    <t>"Bedingung: Wärmeschutz mind. 3"</t>
+    <t>"Ermöglicht: Thermische Flexibilität, Wärmerückgewinnung des Duschwassers"</t>
   </si>
   <si>
-    <t>"Bedingung: Wärmeschutz mind. 5"</t>
+    <t>"Voraussetzung: Private Ladestationen oder Hausweiter E-Car Port."</t>
   </si>
   <si>
-    <t>"Ermöglicht: Thermische Flexibilität, Wärmerückgewinnung des Duschwassers"</t>
+    <t>"Nicht kombinierbar mit Private Ladestationen. Ermöglicht Bi-Direktionelles Laden"</t>
+  </si>
+  <si>
+    <t>Private Ladestationen</t>
+  </si>
+  <si>
+    <t>Ladepunkte machen das Gebäude attraktiver für Nutzer:innen mit E-Autos. Sie steigern den Strombedarf, können aber auch als flexible Speichermöglichkeit genutzt werden (in Kombination mit Bi-Direktionalem Laden")."</t>
+  </si>
+  <si>
+    <t>"Voraussetzung: Keine Fassadenbegrünung"</t>
+  </si>
+  <si>
+    <t>"Voraussetzung: Wärmepumpe"</t>
+  </si>
+  <si>
+    <t>"Effekt: Speicher kann jetzt vom Netz beladen werden. Bei der Wertung des Speichers wird die StromproduktionsVoraussetzung ignoriert."</t>
+  </si>
+  <si>
+    <t>"Voraussetzung: Kein Kleiner Heimspeicher installiert"</t>
+  </si>
+  <si>
+    <t>"Voraussetzung: Kein Großer Batteriespeicher installiert"</t>
+  </si>
+  <si>
+    <t>"Voraussetzung: Keine Fassadenintegrierte PV installiert"</t>
+  </si>
+  <si>
+    <t>"Voraussetzung: Wärmeschutz mind. 3"</t>
+  </si>
+  <si>
+    <t>"Voraussetzung: Wärmeschutz mind. 5"</t>
+  </si>
+  <si>
+    <t>"Eine Grundwasser-Wärmepumpe nutzt die relativ konstante Temperatur des Grundwassers und kann sehr effizient heizen und kühlen. Sie spart viele Emissionen, ist aber teuer, genehmigungspflichtig und nur bei geeigneten StandortVoraussetzungen möglich."</t>
   </si>
 </sst>
 </file>
@@ -3083,7 +3080,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="87">
     <dxf>
@@ -4772,7 +4769,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AJ1002"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
     <col min="3" max="3" width="5.1796875" customWidth="1"/>
@@ -4846,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="R1" s="6" t="s">
         <v>16</v>
@@ -4864,7 +4861,7 @@
         <v>20</v>
       </c>
       <c r="W1" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="X1" s="3" t="s">
         <v>21</v>
@@ -4876,28 +4873,28 @@
         <v>23</v>
       </c>
       <c r="AA1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="AB1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="164" t="s">
+        <v>406</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="AD1" s="164" t="s">
-        <v>409</v>
-      </c>
-      <c r="AE1" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:34" ht="22.5" customHeight="1">
@@ -4946,7 +4943,7 @@
       <c r="U2" s="21"/>
       <c r="V2" s="39"/>
       <c r="W2" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X2" s="40"/>
       <c r="Y2" s="40"/>
@@ -4956,26 +4953,26 @@
         <v>+1SP</v>
       </c>
       <c r="AB2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AC2" s="14" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="AD2" s="166" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="AE2" s="14" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AF2" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG2" s="49"/>
       <c r="AH2" s="49"/>
     </row>
     <row r="3" spans="1:34" ht="22.5" customHeight="1">
       <c r="A3" s="44" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B3" s="34" t="s">
         <v>33</v>
@@ -5019,7 +5016,7 @@
       <c r="U3" s="21"/>
       <c r="V3" s="39"/>
       <c r="W3" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X3" s="43"/>
       <c r="Y3" s="43"/>
@@ -5029,16 +5026,16 @@
         <v>-1EN</v>
       </c>
       <c r="AB3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AC3" s="45" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AD3" s="166" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="AE3" s="62" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AF3" s="45"/>
       <c r="AG3" s="45"/>
@@ -5046,7 +5043,7 @@
     </row>
     <row r="4" spans="1:34" ht="22.5" customHeight="1">
       <c r="A4" s="56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="34" t="s">
         <v>33</v>
@@ -5094,7 +5091,7 @@
       <c r="U4" s="21"/>
       <c r="V4" s="39"/>
       <c r="W4" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X4" s="43"/>
       <c r="Y4" s="43"/>
@@ -5104,26 +5101,26 @@
         <v>-1EN&amp;nbsp;+1BM</v>
       </c>
       <c r="AB4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="AC4" s="132" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="AD4" s="166" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="AE4" s="55" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="AF4" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG4" s="42"/>
       <c r="AH4" s="42"/>
     </row>
     <row r="5" spans="1:34" ht="22.5" customHeight="1">
       <c r="A5" s="58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" s="34" t="s">
         <v>33</v>
@@ -5167,40 +5164,40 @@
       <c r="U5" s="21"/>
       <c r="V5" s="39"/>
       <c r="W5" s="126" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="X5" s="53" t="s">
         <v>0</v>
       </c>
       <c r="Y5" s="53"/>
       <c r="Z5" s="102" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AA5" t="str">
         <f t="shared" si="0"/>
         <v>+4SP</v>
       </c>
       <c r="AB5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AC5" s="52" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="AD5" s="166" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="AE5" s="136" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="AF5" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG5" s="45"/>
       <c r="AH5" s="45"/>
     </row>
     <row r="6" spans="1:34" ht="22.5" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="34" t="s">
         <v>33</v>
@@ -5244,7 +5241,7 @@
       <c r="U6" s="21"/>
       <c r="V6" s="39"/>
       <c r="W6" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X6" s="40"/>
       <c r="Y6" s="40"/>
@@ -5254,19 +5251,19 @@
         <v>-1BM</v>
       </c>
       <c r="AB6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AC6" s="14" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="AD6" s="166" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="AE6" s="14" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AF6" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG6" s="49"/>
       <c r="AH6" s="86">
@@ -5275,7 +5272,7 @@
     </row>
     <row r="7" spans="1:34" ht="22.5" customHeight="1">
       <c r="A7" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B7" s="34" t="s">
         <v>33</v>
@@ -5323,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="82" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="X7" s="53" t="s">
         <v>3</v>
@@ -5337,19 +5334,19 @@
         <v>+1EF</v>
       </c>
       <c r="AB7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AC7" s="64" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="AD7" s="166" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AE7" s="64" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AF7" s="35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG7" s="35"/>
       <c r="AH7" s="35"/>
@@ -5403,13 +5400,13 @@
       <c r="U8" s="21"/>
       <c r="V8" s="39"/>
       <c r="W8" s="82" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="X8" s="32" t="s">
         <v>0</v>
       </c>
       <c r="Y8" s="41" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="Z8" s="171"/>
       <c r="AA8" t="str">
@@ -5417,26 +5414,26 @@
         <v>-2BM&amp;nbsp;+2FL&amp;nbsp;-1ZU</v>
       </c>
       <c r="AB8" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AC8" s="14" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="AD8" s="166" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="AE8" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AF8" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG8" s="49"/>
       <c r="AH8" s="49"/>
     </row>
     <row r="9" spans="1:34" ht="22.5" customHeight="1">
       <c r="A9" s="33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="34" t="s">
         <v>36</v>
@@ -5480,7 +5477,7 @@
       <c r="U9" s="21"/>
       <c r="V9" s="39"/>
       <c r="W9" s="82" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="X9" s="32"/>
       <c r="Y9" s="32"/>
@@ -5490,26 +5487,26 @@
         <v>-1BM</v>
       </c>
       <c r="AB9" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AC9" s="35" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="AD9" s="165" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="AE9" s="167" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="AF9" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG9" s="35"/>
       <c r="AH9" s="35"/>
     </row>
     <row r="10" spans="1:34" ht="22.5" customHeight="1">
       <c r="A10" s="41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>36</v>
@@ -5557,7 +5554,7 @@
       <c r="U10" s="21"/>
       <c r="V10" s="39"/>
       <c r="W10" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X10" s="43"/>
       <c r="Y10" s="43"/>
@@ -5567,26 +5564,26 @@
         <v>+1BM&amp;nbsp;+4FL&amp;nbsp;-1ZU</v>
       </c>
       <c r="AB10" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="AC10" s="42" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="AD10" s="165" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="AE10" s="169" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="AF10" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG10" s="42"/>
       <c r="AH10" s="42"/>
     </row>
     <row r="11" spans="1:34" ht="22.5" customHeight="1">
       <c r="A11" s="54" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B11" s="34" t="s">
         <v>36</v>
@@ -5628,7 +5625,7 @@
       <c r="U11" s="21"/>
       <c r="V11" s="39"/>
       <c r="W11" s="126" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="X11" s="56"/>
       <c r="Y11" s="40"/>
@@ -5638,26 +5635,26 @@
         <v/>
       </c>
       <c r="AB11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AC11" s="141" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="AD11" s="166" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="AE11" s="131" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="AF11" s="45" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AG11" s="45"/>
       <c r="AH11" s="45"/>
     </row>
     <row r="12" spans="1:34" ht="22.5" customHeight="1">
       <c r="A12" s="170" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="34" t="s">
         <v>36</v>
@@ -5703,40 +5700,40 @@
       <c r="U12" s="21"/>
       <c r="V12" s="39"/>
       <c r="W12" s="126" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="X12" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y12" s="43"/>
       <c r="Z12" s="102" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AA12" t="str">
         <f t="shared" si="0"/>
         <v>+5FL</v>
       </c>
       <c r="AB12" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AC12" s="142" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="AD12" s="166" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="AE12" s="132" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="AF12" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG12" s="42"/>
       <c r="AH12" s="42"/>
     </row>
     <row r="13" spans="1:34" ht="22.5" customHeight="1">
       <c r="A13" s="56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B13" s="34" t="s">
         <v>36</v>
@@ -5780,30 +5777,30 @@
       <c r="U13" s="21"/>
       <c r="V13" s="39"/>
       <c r="W13" s="126" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="X13" s="102" t="s">
         <v>0</v>
       </c>
       <c r="Y13" s="40"/>
       <c r="Z13" s="102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AA13" t="str">
         <f t="shared" si="0"/>
         <v>+2FL</v>
       </c>
       <c r="AB13" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="AC13" s="141" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="AD13" s="166" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AE13" s="131" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AF13" s="35"/>
       <c r="AG13" s="35"/>
@@ -5811,7 +5808,7 @@
     </row>
     <row r="14" spans="1:34" ht="22.5" customHeight="1">
       <c r="A14" s="44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B14" s="34" t="s">
         <v>36</v>
@@ -5857,7 +5854,7 @@
       <c r="U14" s="21"/>
       <c r="V14" s="39"/>
       <c r="W14" s="82" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="X14" s="53" t="s">
         <v>3</v>
@@ -5871,26 +5868,26 @@
         <v>+2FL&amp;nbsp;-1ZU</v>
       </c>
       <c r="AB14" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AC14" s="42" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="AD14" s="165" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="AE14" s="169" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="AF14" s="42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG14" s="42"/>
       <c r="AH14" s="42"/>
     </row>
     <row r="15" spans="1:34" ht="22.5" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B15" s="34" t="s">
         <v>31</v>
@@ -5936,7 +5933,7 @@
         <v>1</v>
       </c>
       <c r="W15" s="82" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X15" s="32"/>
       <c r="Y15" s="32"/>
@@ -5946,19 +5943,19 @@
         <v>+1ZU</v>
       </c>
       <c r="AB15" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="AC15" s="49" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="AD15" s="166" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="AE15" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AF15" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG15" s="35"/>
       <c r="AH15" s="35"/>
@@ -6011,7 +6008,7 @@
       <c r="U16" s="21"/>
       <c r="V16" s="39"/>
       <c r="W16" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X16" s="43"/>
       <c r="Y16" s="43"/>
@@ -6021,17 +6018,17 @@
         <v>+1ZU</v>
       </c>
       <c r="AB16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AC16" s="42" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AD16" s="165" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="AE16" s="42"/>
       <c r="AF16" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG16" s="42"/>
       <c r="AH16" s="42"/>
@@ -6082,7 +6079,7 @@
       <c r="U17" s="21"/>
       <c r="V17" s="39"/>
       <c r="W17" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X17" s="43"/>
       <c r="Y17" s="43"/>
@@ -6092,26 +6089,26 @@
         <v>+1ZU</v>
       </c>
       <c r="AB17" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AC17" s="45" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="AD17" s="166" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="AE17" s="52" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="AF17" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG17" s="45"/>
       <c r="AH17" s="45"/>
     </row>
     <row r="18" spans="1:34" ht="22.5" customHeight="1">
       <c r="A18" s="56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="34" t="s">
         <v>31</v>
@@ -6159,40 +6156,40 @@
       <c r="U18" s="21"/>
       <c r="V18" s="39"/>
       <c r="W18" s="126" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X18" s="32" t="s">
         <v>0</v>
       </c>
       <c r="Y18" s="32"/>
       <c r="Z18" s="101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA18" t="str">
         <f t="shared" si="0"/>
         <v>+1ZU</v>
       </c>
       <c r="AB18" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AC18" s="142" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="AD18" s="166" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="AE18" s="132" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AF18" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG18" s="49"/>
       <c r="AH18" s="49"/>
     </row>
     <row r="19" spans="1:34" ht="22.5" customHeight="1">
       <c r="A19" s="41" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B19" s="34" t="s">
         <v>31</v>
@@ -6242,40 +6239,40 @@
       <c r="U19" s="21"/>
       <c r="V19" s="39"/>
       <c r="W19" s="126" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="X19" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y19" s="43"/>
       <c r="Z19" s="53" t="s">
-        <v>350</v>
+        <v>578</v>
       </c>
       <c r="AA19" t="str">
         <f t="shared" si="0"/>
         <v>-6EN&amp;nbsp;+4BM&amp;nbsp;+6FL&amp;nbsp;+2ZU</v>
       </c>
       <c r="AB19" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AC19" s="52" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="AD19" s="166" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="AE19" s="52" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AF19" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG19" s="45"/>
       <c r="AH19" s="45"/>
     </row>
     <row r="20" spans="1:34" ht="22.5" customHeight="1">
       <c r="A20" s="33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>31</v>
@@ -6327,7 +6324,7 @@
       </c>
       <c r="V20" s="39"/>
       <c r="W20" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X20" s="40"/>
       <c r="Y20" s="40"/>
@@ -6337,26 +6334,26 @@
         <v>-1EN</v>
       </c>
       <c r="AB20" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="AC20" s="14" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="AD20" s="166" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="AE20" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AF20" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG20" s="49"/>
       <c r="AH20" s="49"/>
     </row>
     <row r="21" spans="1:34" ht="22.5" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="34" t="s">
         <v>31</v>
@@ -6404,7 +6401,7 @@
       <c r="U21" s="21"/>
       <c r="V21" s="39"/>
       <c r="W21" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X21" s="40"/>
       <c r="Y21" s="40"/>
@@ -6414,26 +6411,26 @@
         <v>+1BM&amp;nbsp;+2ZU</v>
       </c>
       <c r="AB21" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="AC21" s="35" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="AD21" s="166" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="AE21" s="64" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AF21" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG21" s="35"/>
       <c r="AH21" s="35"/>
     </row>
     <row r="22" spans="1:34" ht="22.5" customHeight="1">
       <c r="A22" s="44" t="s">
-        <v>353</v>
+        <v>578</v>
       </c>
       <c r="B22" s="34" t="s">
         <v>31</v>
@@ -6483,47 +6480,47 @@
       <c r="U22" s="21"/>
       <c r="V22" s="39"/>
       <c r="W22" s="126" t="s">
-        <v>586</v>
+        <v>574</v>
       </c>
       <c r="X22" s="43" t="s">
         <v>0</v>
       </c>
       <c r="Y22" s="43"/>
       <c r="Z22" s="41" t="s">
-        <v>37</v>
+        <v>350</v>
       </c>
       <c r="AA22" t="str">
         <f t="shared" si="0"/>
         <v>-3EN&amp;nbsp;+2BM&amp;nbsp;+3FL&amp;nbsp;+1ZU</v>
       </c>
       <c r="AB22" t="s">
-        <v>504</v>
+        <v>579</v>
       </c>
       <c r="AC22" s="42" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="AD22" s="166" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="AE22" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="AF22" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG22" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AH22" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:34" ht="22.5" customHeight="1">
       <c r="A23" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="34" t="s">
         <v>43</v>
-      </c>
-      <c r="B23" s="34" t="s">
-        <v>44</v>
       </c>
       <c r="C23" s="14">
         <v>1</v>
@@ -6568,7 +6565,7 @@
         <v>2</v>
       </c>
       <c r="W23" s="82" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="X23" s="53" t="s">
         <v>10</v>
@@ -6582,19 +6579,19 @@
         <v>+2EF</v>
       </c>
       <c r="AB23" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AC23" s="52" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="AD23" s="166" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AE23" s="52" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AF23" s="45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG23" s="45"/>
       <c r="AH23" s="87">
@@ -6603,10 +6600,10 @@
     </row>
     <row r="24" spans="1:34" ht="22.5" customHeight="1">
       <c r="A24" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B24" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="14">
         <v>1</v>
@@ -6653,7 +6650,7 @@
         <v>2</v>
       </c>
       <c r="W24" s="82" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="X24" s="32" t="s">
         <v>10</v>
@@ -6667,19 +6664,19 @@
         <v>+2EF&amp;nbsp;+1ZU</v>
       </c>
       <c r="AB24" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AC24" s="14" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AD24" s="166" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="AE24" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AF24" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG24" s="49"/>
       <c r="AH24" s="86">
@@ -6688,10 +6685,10 @@
     </row>
     <row r="25" spans="1:34" ht="22.5" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B25" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="14">
         <v>1</v>
@@ -6736,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="W25" s="82" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="X25" s="32" t="s">
         <v>10</v>
@@ -6750,29 +6747,29 @@
         <v>+1EF</v>
       </c>
       <c r="AB25" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AC25" s="137" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AD25" s="166" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="AE25" s="137" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AF25" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG25" s="35"/>
       <c r="AH25" s="35"/>
     </row>
     <row r="26" spans="1:34" ht="22.5" customHeight="1">
       <c r="A26" s="44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" s="14">
         <v>1</v>
@@ -6819,7 +6816,7 @@
         <v>2</v>
       </c>
       <c r="W26" s="82" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="X26" s="53" t="s">
         <v>10</v>
@@ -6833,29 +6830,29 @@
         <v>+1EF&amp;nbsp;-1ZU</v>
       </c>
       <c r="AB26" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AC26" s="139" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="AD26" s="166" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="AE26" s="139" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AF26" s="43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG26" s="42"/>
       <c r="AH26" s="42"/>
     </row>
     <row r="27" spans="1:34" ht="22.5" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="14">
         <v>1</v>
@@ -6900,7 +6897,7 @@
         <v>2</v>
       </c>
       <c r="W27" s="82" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="X27" s="53" t="s">
         <v>10</v>
@@ -6914,29 +6911,29 @@
         <v>+2EF</v>
       </c>
       <c r="AB27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="AC27" s="137" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="AD27" s="166" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AE27" s="137" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AF27" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG27" s="35"/>
       <c r="AH27" s="35"/>
     </row>
     <row r="28" spans="1:34" ht="22.5" customHeight="1">
       <c r="A28" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="34" t="s">
         <v>40</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>41</v>
       </c>
       <c r="C28" s="14">
         <v>1</v>
@@ -6981,7 +6978,7 @@
       <c r="U28" s="21"/>
       <c r="V28" s="39"/>
       <c r="W28" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X28" s="40"/>
       <c r="Y28" s="40"/>
@@ -6991,29 +6988,29 @@
         <v>+1ZU</v>
       </c>
       <c r="AB28" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="AC28" s="140" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AD28" s="166" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AE28" s="140" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF28" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG28" s="49"/>
       <c r="AH28" s="49"/>
     </row>
     <row r="29" spans="1:34" ht="22.5" customHeight="1">
       <c r="A29" s="59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" s="14">
         <v>1</v>
@@ -7054,7 +7051,7 @@
       <c r="U29" s="21"/>
       <c r="V29" s="39"/>
       <c r="W29" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X29" s="40"/>
       <c r="Y29" s="40"/>
@@ -7064,16 +7061,16 @@
         <v>+8SP</v>
       </c>
       <c r="AB29" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AC29" s="35" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AD29" s="166" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AE29" s="64" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AF29" s="35"/>
       <c r="AG29" s="35"/>
@@ -7081,10 +7078,10 @@
     </row>
     <row r="30" spans="1:34" ht="22.5" customHeight="1">
       <c r="A30" s="59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="14">
         <v>1</v>
@@ -7125,7 +7122,7 @@
       <c r="U30" s="21"/>
       <c r="V30" s="39"/>
       <c r="W30" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X30" s="40"/>
       <c r="Y30" s="40"/>
@@ -7135,16 +7132,16 @@
         <v>+2SP</v>
       </c>
       <c r="AB30" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AC30" s="172" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="AD30" s="166" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AE30" s="137" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AF30" s="40"/>
       <c r="AG30" s="49"/>
@@ -7152,10 +7149,10 @@
     </row>
     <row r="31" spans="1:34" ht="22.5" customHeight="1">
       <c r="A31" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" s="14">
         <v>1</v>
@@ -7196,7 +7193,7 @@
       <c r="U31" s="21"/>
       <c r="V31" s="39"/>
       <c r="W31" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X31" s="43"/>
       <c r="Y31" s="43"/>
@@ -7206,16 +7203,16 @@
         <v>+5SP</v>
       </c>
       <c r="AB31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AC31" s="35" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AD31" s="166" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="AE31" s="64" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AF31" s="45"/>
       <c r="AG31" s="45"/>
@@ -7223,10 +7220,10 @@
     </row>
     <row r="32" spans="1:34" ht="22.5" customHeight="1">
       <c r="A32" s="33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="14">
         <v>1</v>
@@ -7267,7 +7264,7 @@
       <c r="U32" s="21"/>
       <c r="V32" s="39"/>
       <c r="W32" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X32" s="40"/>
       <c r="Y32" s="40"/>
@@ -7277,16 +7274,16 @@
         <v>+3SP</v>
       </c>
       <c r="AB32" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AC32" s="14" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AD32" s="166" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AE32" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AF32" s="49"/>
       <c r="AG32" s="49"/>
@@ -7294,10 +7291,10 @@
     </row>
     <row r="33" spans="1:34" ht="22.5" customHeight="1">
       <c r="A33" s="60" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="14">
         <v>1</v>
@@ -7340,7 +7337,7 @@
       <c r="U33" s="21"/>
       <c r="V33" s="39"/>
       <c r="W33" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X33" s="43"/>
       <c r="Y33" s="43"/>
@@ -7350,16 +7347,16 @@
         <v>+2SP&amp;nbsp;+1ZU</v>
       </c>
       <c r="AB33" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AC33" s="52" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AD33" s="166" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="AE33" s="52" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AF33" s="45"/>
       <c r="AG33" s="45"/>
@@ -7367,10 +7364,10 @@
     </row>
     <row r="34" spans="1:34" ht="22.5" customHeight="1">
       <c r="A34" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B34" s="62" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" s="14">
         <v>1</v>
@@ -7415,7 +7412,7 @@
       </c>
       <c r="V34" s="39"/>
       <c r="W34" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X34" s="43"/>
       <c r="Y34" s="43"/>
@@ -7425,16 +7422,16 @@
         <v>+1WS</v>
       </c>
       <c r="AB34" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AC34" s="55" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AD34" s="166" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AE34" s="55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AF34" s="42"/>
       <c r="AG34" s="42"/>
@@ -7494,7 +7491,7 @@
       </c>
       <c r="V35" s="39"/>
       <c r="W35" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X35" s="40"/>
       <c r="Y35" s="40"/>
@@ -7504,22 +7501,22 @@
         <v>+4WS</v>
       </c>
       <c r="AB35" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="AC35" s="64" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AD35" s="166" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="AE35" s="64" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF35" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG35" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH35" s="153">
         <v>11</v>
@@ -7577,7 +7574,7 @@
       </c>
       <c r="V36" s="39"/>
       <c r="W36" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X36" s="43"/>
       <c r="Y36" s="43"/>
@@ -7587,22 +7584,22 @@
         <v>+4WS</v>
       </c>
       <c r="AB36" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AC36" s="55" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AD36" s="166" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AE36" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF36" s="143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG36" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH36" s="152">
         <v>11</v>
@@ -7610,7 +7607,7 @@
     </row>
     <row r="37" spans="1:34" ht="22.5" customHeight="1">
       <c r="A37" s="56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="62" t="s">
         <v>28</v>
@@ -7658,7 +7655,7 @@
       </c>
       <c r="V37" s="39"/>
       <c r="W37" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X37" s="40"/>
       <c r="Y37" s="40"/>
@@ -7668,26 +7665,26 @@
         <v>+1WS</v>
       </c>
       <c r="AB37" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AC37" s="131" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="AD37" s="166" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AE37" s="131" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AF37" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG37" s="35"/>
       <c r="AH37" s="35"/>
     </row>
     <row r="38" spans="1:34" ht="22.5" customHeight="1">
       <c r="A38" s="33" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B38" s="62" t="s">
         <v>28</v>
@@ -7735,7 +7732,7 @@
       </c>
       <c r="V38" s="39"/>
       <c r="W38" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X38" s="40"/>
       <c r="Y38" s="40"/>
@@ -7745,20 +7742,20 @@
         <v>+2WS</v>
       </c>
       <c r="AB38" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AC38" s="14" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AD38" s="166" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="AE38" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AF38" s="88"/>
       <c r="AG38" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH38" s="86">
         <v>12</v>
@@ -7766,7 +7763,7 @@
     </row>
     <row r="39" spans="1:34" ht="22.5" customHeight="1">
       <c r="A39" s="41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>28</v>
@@ -7814,7 +7811,7 @@
       </c>
       <c r="V39" s="39"/>
       <c r="W39" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X39" s="43"/>
       <c r="Y39" s="43"/>
@@ -7824,22 +7821,22 @@
         <v>+2WS</v>
       </c>
       <c r="AB39" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AC39" s="52" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AD39" s="166" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="AE39" s="52" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AF39" s="89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG39" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH39" s="87">
         <v>13</v>
@@ -7847,7 +7844,7 @@
     </row>
     <row r="40" spans="1:34" ht="22.5" customHeight="1">
       <c r="A40" s="44" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B40" s="34" t="s">
         <v>28</v>
@@ -7895,7 +7892,7 @@
       </c>
       <c r="V40" s="39"/>
       <c r="W40" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X40" s="43"/>
       <c r="Y40" s="43"/>
@@ -7905,20 +7902,20 @@
         <v>+2WS</v>
       </c>
       <c r="AB40" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AC40" s="133" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AD40" s="166" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="AE40" s="133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AF40" s="146"/>
       <c r="AG40" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH40" s="152">
         <v>12</v>
@@ -7926,7 +7923,7 @@
     </row>
     <row r="41" spans="1:34" ht="22.5" customHeight="1">
       <c r="A41" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>28</v>
@@ -7974,7 +7971,7 @@
       </c>
       <c r="V41" s="39"/>
       <c r="W41" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X41" s="40"/>
       <c r="Y41" s="40"/>
@@ -7984,22 +7981,22 @@
         <v>+2WS</v>
       </c>
       <c r="AB41" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AC41" s="140" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AD41" s="166" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AE41" s="140" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AF41" s="148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG41" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH41" s="153">
         <v>13</v>
@@ -8007,7 +8004,7 @@
     </row>
     <row r="42" spans="1:34" ht="22.5" customHeight="1">
       <c r="A42" s="44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B42" s="34" t="s">
         <v>28</v>
@@ -8057,7 +8054,7 @@
       </c>
       <c r="V42" s="39"/>
       <c r="W42" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X42" s="43"/>
       <c r="Y42" s="43"/>
@@ -8067,20 +8064,20 @@
         <v>+5WS</v>
       </c>
       <c r="AB42" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AC42" s="53" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="AD42" s="166" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AE42" s="53" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AF42" s="146"/>
       <c r="AG42" s="146" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH42" s="155">
         <v>11</v>
@@ -8088,7 +8085,7 @@
     </row>
     <row r="43" spans="1:34" ht="22.5" customHeight="1">
       <c r="A43" s="61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B43" s="34" t="s">
         <v>28</v>
@@ -8137,7 +8134,7 @@
       </c>
       <c r="V43" s="39"/>
       <c r="W43" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X43" s="40"/>
       <c r="Y43" s="40"/>
@@ -8147,20 +8144,20 @@
         <v>+5WS</v>
       </c>
       <c r="AB43" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AC43" s="14" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AD43" s="166" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AE43" s="55" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="AF43" s="88"/>
       <c r="AG43" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH43" s="86">
         <v>11</v>
@@ -8168,7 +8165,7 @@
     </row>
     <row r="44" spans="1:34" ht="22.5" customHeight="1">
       <c r="A44" s="100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" s="34" t="s">
         <v>28</v>
@@ -8212,7 +8209,7 @@
       <c r="U44" s="21"/>
       <c r="V44" s="39"/>
       <c r="W44" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X44" s="43"/>
       <c r="Y44" s="43"/>
@@ -8222,26 +8219,26 @@
         <v/>
       </c>
       <c r="AB44" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AC44" s="45" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="AD44" s="165" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="AE44" s="168" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="AF44" s="89"/>
       <c r="AG44" s="89" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AH44" s="45"/>
     </row>
     <row r="45" spans="1:34" ht="22.5" customHeight="1">
       <c r="A45" s="57" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B45" s="34" t="s">
         <v>28</v>
@@ -8289,7 +8286,7 @@
       </c>
       <c r="V45" s="39"/>
       <c r="W45" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X45" s="43"/>
       <c r="Y45" s="43"/>
@@ -8299,26 +8296,26 @@
         <v>+2WS</v>
       </c>
       <c r="AB45" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AC45" s="129" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="AD45" s="166" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AE45" s="129" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AF45" s="151"/>
       <c r="AG45" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH45" s="42"/>
     </row>
     <row r="46" spans="1:34" ht="22.5" customHeight="1">
       <c r="A46" s="59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B46" s="34" t="s">
         <v>28</v>
@@ -8366,7 +8363,7 @@
       </c>
       <c r="V46" s="39"/>
       <c r="W46" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X46" s="40"/>
       <c r="Y46" s="40"/>
@@ -8376,20 +8373,20 @@
         <v>+2WS</v>
       </c>
       <c r="AB46" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AC46" s="140" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="AD46" s="166" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AE46" s="64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AF46" s="148"/>
       <c r="AG46" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH46" s="153">
         <v>12</v>
@@ -8397,7 +8394,7 @@
     </row>
     <row r="47" spans="1:34" ht="22.5" customHeight="1">
       <c r="A47" s="41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>28</v>
@@ -8445,7 +8442,7 @@
       </c>
       <c r="V47" s="39"/>
       <c r="W47" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X47" s="43"/>
       <c r="Y47" s="43"/>
@@ -8455,20 +8452,20 @@
         <v>+2WS</v>
       </c>
       <c r="AB47" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AC47" s="55" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AD47" s="166" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AE47" s="55" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AF47" s="143"/>
       <c r="AG47" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH47" s="152">
         <v>13</v>
@@ -8476,7 +8473,7 @@
     </row>
     <row r="48" spans="1:34" ht="22.5" customHeight="1">
       <c r="A48" s="100" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B48" s="34" t="s">
         <v>28</v>
@@ -8526,7 +8523,7 @@
       </c>
       <c r="V48" s="39"/>
       <c r="W48" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X48" s="43"/>
       <c r="Y48" s="43"/>
@@ -8536,20 +8533,20 @@
         <v>+3WS</v>
       </c>
       <c r="AB48" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AC48" s="52" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="AD48" s="166" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="AE48" s="52" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AF48" s="89"/>
       <c r="AG48" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH48" s="87">
         <v>11</v>
@@ -8557,7 +8554,7 @@
     </row>
     <row r="49" spans="1:34" ht="22.5" customHeight="1">
       <c r="A49" s="12" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" s="34" t="s">
         <v>28</v>
@@ -8606,7 +8603,7 @@
       </c>
       <c r="V49" s="39"/>
       <c r="W49" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X49" s="40"/>
       <c r="Y49" s="40"/>
@@ -8616,20 +8613,20 @@
         <v>+3WS</v>
       </c>
       <c r="AB49" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AC49" s="14" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AD49" s="166" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="AE49" s="14" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="AF49" s="88"/>
       <c r="AG49" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH49" s="86">
         <v>11</v>
@@ -8637,7 +8634,7 @@
     </row>
     <row r="50" spans="1:34" ht="22.5" customHeight="1">
       <c r="A50" s="58" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B50" s="62" t="s">
         <v>28</v>
@@ -8685,7 +8682,7 @@
       </c>
       <c r="V50" s="39"/>
       <c r="W50" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X50" s="43"/>
       <c r="Y50" s="43"/>
@@ -8695,20 +8692,20 @@
         <v>+1WS</v>
       </c>
       <c r="AB50" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AC50" s="136" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="AD50" s="166" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AE50" s="136" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AF50" s="150"/>
       <c r="AG50" s="89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH50" s="87">
         <v>20</v>
@@ -8716,7 +8713,7 @@
     </row>
     <row r="51" spans="1:34" ht="22.5" customHeight="1">
       <c r="A51" s="57" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B51" s="62" t="s">
         <v>28</v>
@@ -8764,7 +8761,7 @@
       </c>
       <c r="V51" s="39"/>
       <c r="W51" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X51" s="40"/>
       <c r="Y51" s="40"/>
@@ -8774,20 +8771,20 @@
         <v>+1WS</v>
       </c>
       <c r="AB51" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AC51" s="129" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="AD51" s="166" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AE51" s="129" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AF51" s="145"/>
       <c r="AG51" s="88" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH51" s="86">
         <v>21</v>
@@ -8795,7 +8792,7 @@
     </row>
     <row r="52" spans="1:34" ht="22.5" customHeight="1">
       <c r="A52" s="58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B52" s="62" t="s">
         <v>28</v>
@@ -8843,7 +8840,7 @@
       </c>
       <c r="V52" s="39"/>
       <c r="W52" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X52" s="40"/>
       <c r="Y52" s="40"/>
@@ -8853,20 +8850,20 @@
         <v>+2WS</v>
       </c>
       <c r="AB52" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AC52" s="173" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AD52" s="166" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="AE52" s="129" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AF52" s="174"/>
       <c r="AG52" s="144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH52" s="153">
         <v>9</v>
@@ -8874,7 +8871,7 @@
     </row>
     <row r="53" spans="1:34" ht="22.5" customHeight="1">
       <c r="A53" s="41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B53" s="62" t="s">
         <v>28</v>
@@ -8922,7 +8919,7 @@
       </c>
       <c r="V53" s="39"/>
       <c r="W53" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X53" s="43"/>
       <c r="Y53" s="43"/>
@@ -8932,20 +8929,20 @@
         <v>+2WS</v>
       </c>
       <c r="AB53" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AC53" s="55" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="AD53" s="166" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="AE53" s="55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF53" s="143"/>
       <c r="AG53" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH53" s="152">
         <v>12</v>
@@ -8953,7 +8950,7 @@
     </row>
     <row r="54" spans="1:34" ht="22.5" customHeight="1">
       <c r="A54" s="59" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B54" s="63" t="s">
         <v>28</v>
@@ -9001,7 +8998,7 @@
       </c>
       <c r="V54" s="39"/>
       <c r="W54" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X54" s="40"/>
       <c r="Y54" s="40"/>
@@ -9011,20 +9008,20 @@
         <v>+2WS</v>
       </c>
       <c r="AB54" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AC54" s="64" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="AD54" s="166" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="AE54" s="64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AF54" s="144"/>
       <c r="AG54" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH54" s="153">
         <v>13</v>
@@ -9032,10 +9029,10 @@
     </row>
     <row r="55" spans="1:34" ht="22.5" customHeight="1">
       <c r="A55" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="63" t="s">
         <v>54</v>
-      </c>
-      <c r="B55" s="63" t="s">
-        <v>55</v>
       </c>
       <c r="C55" s="14">
         <v>1</v>
@@ -9082,7 +9079,7 @@
       </c>
       <c r="V55" s="39"/>
       <c r="W55" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X55" s="43"/>
       <c r="Y55" s="43"/>
@@ -9092,29 +9089,29 @@
         <v>+2WS</v>
       </c>
       <c r="AB55" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AC55" s="55" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AD55" s="166" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="AE55" s="55" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF55" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG55" s="42"/>
       <c r="AH55" s="42"/>
     </row>
     <row r="56" spans="1:34" ht="22.5" customHeight="1">
       <c r="A56" s="33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56" s="63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C56" s="14">
         <v>1</v>
@@ -9161,7 +9158,7 @@
       </c>
       <c r="V56" s="39"/>
       <c r="W56" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X56" s="40"/>
       <c r="Y56" s="40"/>
@@ -9171,29 +9168,29 @@
         <v>+3WS</v>
       </c>
       <c r="AB56" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AC56" s="137" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AD56" s="166" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="AE56" s="137" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF56" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG56" s="35"/>
       <c r="AH56" s="35"/>
     </row>
     <row r="57" spans="1:34" ht="22.5" customHeight="1">
       <c r="A57" s="41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57" s="63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C57" s="14">
         <v>1</v>
@@ -9240,7 +9237,7 @@
       </c>
       <c r="V57" s="39"/>
       <c r="W57" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X57" s="43"/>
       <c r="Y57" s="43"/>
@@ -9250,29 +9247,29 @@
         <v>+3WS</v>
       </c>
       <c r="AB57" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AC57" s="139" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AD57" s="166" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="AE57" s="139" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF57" s="43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG57" s="42"/>
       <c r="AH57" s="42"/>
     </row>
     <row r="58" spans="1:34" ht="22.5" customHeight="1">
       <c r="A58" s="59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58" s="63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C58" s="14">
         <v>1</v>
@@ -9319,7 +9316,7 @@
       </c>
       <c r="V58" s="39"/>
       <c r="W58" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X58" s="40"/>
       <c r="Y58" s="40"/>
@@ -9329,29 +9326,29 @@
         <v>+2WS</v>
       </c>
       <c r="AB58" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AC58" s="64" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="AD58" s="166" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="AE58" s="64" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF58" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG58" s="35"/>
       <c r="AH58" s="35"/>
     </row>
     <row r="59" spans="1:34" ht="22.5" customHeight="1">
       <c r="A59" s="60" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B59" s="63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C59" s="14">
         <v>1</v>
@@ -9396,7 +9393,7 @@
       </c>
       <c r="V59" s="39"/>
       <c r="W59" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X59" s="43"/>
       <c r="Y59" s="43"/>
@@ -9406,29 +9403,29 @@
         <v>+1WS</v>
       </c>
       <c r="AB59" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AC59" s="55" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="AD59" s="166" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="AE59" s="55" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AF59" s="143"/>
       <c r="AG59" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH59" s="42"/>
     </row>
     <row r="60" spans="1:34" ht="22.5" customHeight="1">
       <c r="A60" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B60" s="63" t="s">
         <v>45</v>
-      </c>
-      <c r="B60" s="63" t="s">
-        <v>46</v>
       </c>
       <c r="C60" s="14">
         <v>1</v>
@@ -9473,7 +9470,7 @@
       </c>
       <c r="V60" s="39"/>
       <c r="W60" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X60" s="40"/>
       <c r="Y60" s="40"/>
@@ -9483,22 +9480,22 @@
         <v>+1WS</v>
       </c>
       <c r="AB60" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AC60" s="64" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="AD60" s="166" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="AE60" s="64" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AF60" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG60" s="144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH60" s="153">
         <v>27</v>
@@ -9506,10 +9503,10 @@
     </row>
     <row r="61" spans="1:34" ht="22.5" customHeight="1">
       <c r="A61" s="57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B61" s="63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C61" s="14">
         <v>0</v>
@@ -9554,7 +9551,7 @@
       </c>
       <c r="V61" s="39"/>
       <c r="W61" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X61" s="40"/>
       <c r="Y61" s="40"/>
@@ -9564,22 +9561,22 @@
         <v>+1WS</v>
       </c>
       <c r="AB61" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AC61" s="129" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="AD61" s="166" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="AE61" s="129" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AF61" s="145" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG61" s="88" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH61" s="86">
         <v>29</v>
@@ -9587,10 +9584,10 @@
     </row>
     <row r="62" spans="1:34" ht="22.5" customHeight="1">
       <c r="A62" s="33" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B62" s="63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="14">
         <v>1</v>
@@ -9639,7 +9636,7 @@
       </c>
       <c r="V62" s="39"/>
       <c r="W62" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X62" s="40"/>
       <c r="Y62" s="40"/>
@@ -9649,22 +9646,22 @@
         <v>+1BM&amp;nbsp;+2WS&amp;nbsp;+1ZU</v>
       </c>
       <c r="AB62" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AC62" s="64" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AD62" s="166" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="AE62" s="64" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="AF62" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG62" s="144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH62" s="153">
         <v>24</v>
@@ -9672,10 +9669,10 @@
     </row>
     <row r="63" spans="1:34" ht="22.5" customHeight="1">
       <c r="A63" s="57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="14">
         <v>0</v>
@@ -9720,7 +9717,7 @@
       </c>
       <c r="V63" s="39"/>
       <c r="W63" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X63" s="43"/>
       <c r="Y63" s="43"/>
@@ -9730,22 +9727,22 @@
         <v>+1WS</v>
       </c>
       <c r="AB63" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AC63" s="129" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="AD63" s="166" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="AE63" s="129" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AF63" s="151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG63" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH63" s="152">
         <v>26</v>
@@ -9753,10 +9750,10 @@
     </row>
     <row r="64" spans="1:34" ht="22.5" customHeight="1">
       <c r="A64" s="57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B64" s="63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C64" s="14">
         <v>1</v>
@@ -9803,7 +9800,7 @@
       </c>
       <c r="V64" s="39"/>
       <c r="W64" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X64" s="43"/>
       <c r="Y64" s="43"/>
@@ -9813,22 +9810,22 @@
         <v>+1ZU</v>
       </c>
       <c r="AB64" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AC64" s="129" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="AD64" s="166" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="AE64" s="129" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF64" s="151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG64" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH64" s="152">
         <v>30</v>
@@ -9836,10 +9833,10 @@
     </row>
     <row r="65" spans="1:34" ht="22.5" customHeight="1">
       <c r="A65" s="44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" s="63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C65" s="14">
         <v>1</v>
@@ -9888,7 +9885,7 @@
       </c>
       <c r="V65" s="39"/>
       <c r="W65" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X65" s="43"/>
       <c r="Y65" s="43"/>
@@ -9898,20 +9895,20 @@
         <v>+1BM&amp;nbsp;+1WS&amp;nbsp;+1ZU</v>
       </c>
       <c r="AB65" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AC65" s="52" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="AD65" s="166" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="AE65" s="52" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AF65" s="89"/>
       <c r="AG65" s="89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AH65" s="87">
         <v>24</v>
@@ -9969,7 +9966,7 @@
         <v>2</v>
       </c>
       <c r="W66" s="82" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="X66" s="32"/>
       <c r="Y66" s="53"/>
@@ -9979,22 +9976,22 @@
         <v>+2EF&amp;nbsp;WP</v>
       </c>
       <c r="AB66" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="AC66" s="140" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="AD66" s="166" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="AE66" s="140" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AF66" s="148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG66" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH66" s="86">
         <v>31</v>
@@ -10002,7 +9999,7 @@
     </row>
     <row r="67" spans="1:34" ht="22.5" customHeight="1">
       <c r="A67" s="44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B67" s="63" t="s">
         <v>25</v>
@@ -10011,7 +10008,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E67" s="15">
         <v>1</v>
@@ -10050,7 +10047,7 @@
       <c r="U67" s="21"/>
       <c r="V67" s="39"/>
       <c r="W67" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X67" s="53"/>
       <c r="Z67" s="53"/>
@@ -10059,22 +10056,22 @@
         <v>-1ZU&amp;nbsp;BIO</v>
       </c>
       <c r="AB67" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="AC67" s="52" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="AD67" s="166" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="AE67" s="52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AF67" s="89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG67" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH67" s="87">
         <v>25</v>
@@ -10082,7 +10079,7 @@
     </row>
     <row r="68" spans="1:34" ht="22.5" customHeight="1">
       <c r="A68" s="100" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B68" s="13" t="s">
         <v>25</v>
@@ -10136,7 +10133,7 @@
         <v>1</v>
       </c>
       <c r="W68" s="82" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X68" s="53"/>
       <c r="Y68" s="53"/>
@@ -10146,22 +10143,22 @@
         <v>+1EF&amp;nbsp;-1ZU&amp;nbsp;WP</v>
       </c>
       <c r="AB68" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AC68" s="55" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="AD68" s="166" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="AE68" s="55" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AF68" s="143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG68" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH68" s="152">
         <v>29</v>
@@ -10169,7 +10166,7 @@
     </row>
     <row r="69" spans="1:34" ht="22.5" customHeight="1">
       <c r="A69" s="44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B69" s="13" t="s">
         <v>25</v>
@@ -10223,7 +10220,7 @@
         <v>2</v>
       </c>
       <c r="W69" s="82" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="X69" s="53"/>
       <c r="Y69" s="53"/>
@@ -10233,22 +10230,22 @@
         <v>+2EF&amp;nbsp;WP</v>
       </c>
       <c r="AB69" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AC69" s="52" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="AD69" s="166" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="AE69" s="52" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AF69" s="89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG69" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH69" s="87">
         <v>26</v>
@@ -10256,7 +10253,7 @@
     </row>
     <row r="70" spans="1:34" ht="22.5" customHeight="1">
       <c r="A70" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="13" t="s">
         <v>25</v>
@@ -10265,7 +10262,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E70" s="15">
         <v>1</v>
@@ -10302,7 +10299,7 @@
       <c r="U70" s="21"/>
       <c r="V70" s="39"/>
       <c r="W70" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X70" s="32"/>
       <c r="Y70" s="32"/>
@@ -10312,22 +10309,22 @@
         <v>FW</v>
       </c>
       <c r="AB70" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="AC70" s="14" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="AD70" s="166" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="AE70" s="14" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="AF70" s="88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG70" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH70" s="86">
         <v>24</v>
@@ -10335,7 +10332,7 @@
     </row>
     <row r="71" spans="1:34" ht="22.5" customHeight="1">
       <c r="A71" s="33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B71" s="13" t="s">
         <v>25</v>
@@ -10387,7 +10384,7 @@
         <v>2</v>
       </c>
       <c r="W71" s="82" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="X71" s="32"/>
       <c r="Y71" s="32"/>
@@ -10397,22 +10394,22 @@
         <v>+2EF&amp;nbsp;WP</v>
       </c>
       <c r="AB71" t="s">
-        <v>405</v>
+        <v>588</v>
       </c>
       <c r="AC71" s="64" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AD71" s="166" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AE71" s="64" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="AF71" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG71" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH71" s="153">
         <v>27</v>
@@ -10420,7 +10417,7 @@
     </row>
     <row r="72" spans="1:34" ht="22.5" customHeight="1">
       <c r="A72" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>25</v>
@@ -10429,7 +10426,7 @@
         <v>1</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E72" s="65">
         <v>2</v>
@@ -10466,7 +10463,7 @@
       <c r="U72" s="21"/>
       <c r="V72" s="39"/>
       <c r="W72" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X72" s="32"/>
       <c r="Y72" s="32"/>
@@ -10476,22 +10473,22 @@
         <v>GG</v>
       </c>
       <c r="AB72" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="AC72" s="35" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AD72" s="166" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="AE72" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AF72" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG72" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH72" s="153">
         <v>32</v>
@@ -10499,7 +10496,7 @@
     </row>
     <row r="73" spans="1:34" ht="22.5" customHeight="1">
       <c r="A73" s="44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>25</v>
@@ -10543,7 +10540,7 @@
       <c r="U73" s="21"/>
       <c r="V73" s="39"/>
       <c r="W73" s="126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X73" s="43"/>
       <c r="Y73" s="43"/>
@@ -10553,19 +10550,19 @@
         <v/>
       </c>
       <c r="AB73" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="AC73" s="53" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="AD73" s="166" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AE73" s="135" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF73" s="43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG73" s="43"/>
       <c r="AH73" s="155">
@@ -10574,7 +10571,7 @@
     </row>
     <row r="74" spans="1:34" ht="22.5" customHeight="1">
       <c r="A74" s="66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B74" s="13" t="s">
         <v>25</v>
@@ -10626,7 +10623,7 @@
         <v>1</v>
       </c>
       <c r="W74" s="82" t="s">
-        <v>589</v>
+        <v>575</v>
       </c>
       <c r="X74" s="53"/>
       <c r="Y74" s="53"/>
@@ -10636,22 +10633,22 @@
         <v>+1EF&amp;nbsp;WP</v>
       </c>
       <c r="AB74" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AC74" s="67" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AD74" s="166" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="AE74" s="67" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AF74" s="147" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="AG74" s="147" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AH74" s="154">
         <v>28</v>
@@ -10681,7 +10678,7 @@
       <c r="U75" s="30"/>
       <c r="V75" s="31"/>
       <c r="W75" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X75" s="32"/>
       <c r="Y75" s="32"/>
@@ -10717,7 +10714,7 @@
       <c r="U76" s="30"/>
       <c r="V76" s="31"/>
       <c r="W76" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X76" s="32"/>
       <c r="Y76" s="32"/>
@@ -10753,7 +10750,7 @@
       <c r="U77" s="30"/>
       <c r="V77" s="31"/>
       <c r="W77" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X77" s="32"/>
       <c r="Y77" s="32"/>
@@ -10789,7 +10786,7 @@
       <c r="U78" s="30"/>
       <c r="V78" s="31"/>
       <c r="W78" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X78" s="32"/>
       <c r="Y78" s="32"/>
@@ -10825,7 +10822,7 @@
       <c r="U79" s="30"/>
       <c r="V79" s="31"/>
       <c r="W79" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X79" s="32"/>
       <c r="Y79" s="32"/>
@@ -10861,7 +10858,7 @@
       <c r="U80" s="30"/>
       <c r="V80" s="31"/>
       <c r="W80" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X80" s="32"/>
       <c r="Y80" s="32"/>
@@ -10897,7 +10894,7 @@
       <c r="U81" s="30"/>
       <c r="V81" s="31"/>
       <c r="W81" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X81" s="32"/>
       <c r="Y81" s="32"/>
@@ -10933,7 +10930,7 @@
       <c r="U82" s="30"/>
       <c r="V82" s="31"/>
       <c r="W82" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X82" s="32"/>
       <c r="Y82" s="32"/>
@@ -10969,7 +10966,7 @@
       <c r="U83" s="30"/>
       <c r="V83" s="31"/>
       <c r="W83" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X83" s="32"/>
       <c r="Y83" s="32"/>
@@ -11005,7 +11002,7 @@
       <c r="U84" s="30"/>
       <c r="V84" s="31"/>
       <c r="W84" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X84" s="32"/>
       <c r="Y84" s="32"/>
@@ -11041,7 +11038,7 @@
       <c r="U85" s="30"/>
       <c r="V85" s="31"/>
       <c r="W85" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X85" s="32"/>
       <c r="Y85" s="32"/>
@@ -11077,7 +11074,7 @@
       <c r="U86" s="30"/>
       <c r="V86" s="31"/>
       <c r="W86" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X86" s="32"/>
       <c r="Y86" s="32"/>
@@ -11113,7 +11110,7 @@
       <c r="U87" s="30"/>
       <c r="V87" s="31"/>
       <c r="W87" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X87" s="32"/>
       <c r="Y87" s="32"/>
@@ -11149,7 +11146,7 @@
       <c r="U88" s="30"/>
       <c r="V88" s="31"/>
       <c r="W88" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X88" s="32"/>
       <c r="Y88" s="32"/>
@@ -11185,7 +11182,7 @@
       <c r="U89" s="30"/>
       <c r="V89" s="31"/>
       <c r="W89" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X89" s="32"/>
       <c r="Y89" s="32"/>
@@ -11221,7 +11218,7 @@
       <c r="U90" s="30"/>
       <c r="V90" s="31"/>
       <c r="W90" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X90" s="32"/>
       <c r="Y90" s="32"/>
@@ -11257,7 +11254,7 @@
       <c r="U91" s="30"/>
       <c r="V91" s="31"/>
       <c r="W91" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X91" s="32"/>
       <c r="Y91" s="32"/>
@@ -11293,7 +11290,7 @@
       <c r="U92" s="30"/>
       <c r="V92" s="31"/>
       <c r="W92" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X92" s="32"/>
       <c r="Y92" s="32"/>
@@ -11329,7 +11326,7 @@
       <c r="U93" s="30"/>
       <c r="V93" s="31"/>
       <c r="W93" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X93" s="32"/>
       <c r="Y93" s="32"/>
@@ -11365,7 +11362,7 @@
       <c r="U94" s="30"/>
       <c r="V94" s="31"/>
       <c r="W94" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X94" s="32"/>
       <c r="Y94" s="32"/>
@@ -11401,7 +11398,7 @@
       <c r="U95" s="30"/>
       <c r="V95" s="31"/>
       <c r="W95" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X95" s="32"/>
       <c r="Y95" s="32"/>
@@ -11437,7 +11434,7 @@
       <c r="U96" s="30"/>
       <c r="V96" s="31"/>
       <c r="W96" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X96" s="32"/>
       <c r="Y96" s="32"/>
@@ -11473,7 +11470,7 @@
       <c r="U97" s="30"/>
       <c r="V97" s="31"/>
       <c r="W97" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X97" s="32"/>
       <c r="Y97" s="32"/>
@@ -11509,7 +11506,7 @@
       <c r="U98" s="30"/>
       <c r="V98" s="31"/>
       <c r="W98" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X98" s="32"/>
       <c r="Y98" s="32"/>
@@ -11545,7 +11542,7 @@
       <c r="U99" s="30"/>
       <c r="V99" s="31"/>
       <c r="W99" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X99" s="32"/>
       <c r="Y99" s="32"/>
@@ -11581,7 +11578,7 @@
       <c r="U100" s="30"/>
       <c r="V100" s="31"/>
       <c r="W100" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X100" s="32"/>
       <c r="Y100" s="32"/>
@@ -11617,7 +11614,7 @@
       <c r="U101" s="30"/>
       <c r="V101" s="31"/>
       <c r="W101" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X101" s="32"/>
       <c r="Y101" s="32"/>
@@ -11653,7 +11650,7 @@
       <c r="U102" s="30"/>
       <c r="V102" s="31"/>
       <c r="W102" s="31" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="X102" s="32"/>
       <c r="Y102" s="32"/>
@@ -39606,7 +39603,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:V996"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.453125" customWidth="1"/>
     <col min="2" max="4" width="35.1796875" customWidth="1"/>
@@ -39621,25 +39618,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="I1" s="83"/>
       <c r="J1" s="83"/>
@@ -39661,19 +39658,19 @@
         <v>24</v>
       </c>
       <c r="B2" s="14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>237</v>
-      </c>
       <c r="E2" s="88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F2" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G2" s="86">
         <v>31</v>
@@ -39699,19 +39696,19 @@
         <v>27</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="144" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3" s="144" t="s">
         <v>129</v>
-      </c>
-      <c r="E3" s="144" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" s="144" t="s">
-        <v>130</v>
       </c>
       <c r="G3" s="153">
         <v>11</v>
@@ -39737,19 +39734,19 @@
         <v>29</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D4" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="E4" s="143" t="s">
+        <v>138</v>
+      </c>
+      <c r="F4" s="143" t="s">
         <v>129</v>
-      </c>
-      <c r="E4" s="143" t="s">
-        <v>139</v>
-      </c>
-      <c r="F4" s="143" t="s">
-        <v>130</v>
       </c>
       <c r="G4" s="152">
         <v>11</v>
@@ -39772,17 +39769,17 @@
     </row>
     <row r="5" spans="1:22" ht="22.5" customHeight="1">
       <c r="A5" s="33" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B5" s="64" t="s">
+        <v>264</v>
+      </c>
+      <c r="C5" s="64" t="s">
         <v>265</v>
-      </c>
-      <c r="C5" s="64" t="s">
-        <v>266</v>
       </c>
       <c r="D5" s="35"/>
       <c r="E5" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="35"/>
       <c r="G5" s="35"/>
@@ -39808,11 +39805,11 @@
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="55" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
@@ -39837,16 +39834,16 @@
         <v>32</v>
       </c>
       <c r="B7" s="64" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="64" t="s">
         <v>193</v>
       </c>
-      <c r="C7" s="64" t="s">
+      <c r="D7" s="64" t="s">
         <v>194</v>
       </c>
-      <c r="D7" s="64" t="s">
-        <v>195</v>
-      </c>
       <c r="E7" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F7" s="35"/>
       <c r="G7" s="35"/>
@@ -39871,14 +39868,14 @@
         <v>34</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C8" s="55" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F8" s="42"/>
       <c r="G8" s="42"/>
@@ -39903,16 +39900,16 @@
         <v>35</v>
       </c>
       <c r="B9" s="64" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="64" t="s">
         <v>183</v>
       </c>
-      <c r="C9" s="64" t="s">
+      <c r="D9" s="64" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="64" t="s">
-        <v>185</v>
-      </c>
       <c r="E9" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F9" s="35"/>
       <c r="G9" s="35"/>
@@ -39934,22 +39931,22 @@
     </row>
     <row r="10" spans="1:22" ht="22.5" customHeight="1">
       <c r="A10" s="41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="55" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="55" t="s">
         <v>232</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="D10" s="55" t="s">
         <v>233</v>
       </c>
-      <c r="D10" s="55" t="s">
-        <v>234</v>
-      </c>
       <c r="E10" s="143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F10" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G10" s="152">
         <v>25</v>
@@ -39972,13 +39969,13 @@
     </row>
     <row r="11" spans="1:22" ht="22.5" customHeight="1">
       <c r="A11" s="44" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B11" s="62" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D11" s="45"/>
       <c r="E11" s="45"/>
@@ -40002,19 +39999,19 @@
     </row>
     <row r="12" spans="1:22" ht="22.5" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="E12" s="49" t="s">
         <v>138</v>
-      </c>
-      <c r="E12" s="49" t="s">
-        <v>139</v>
       </c>
       <c r="F12" s="49"/>
       <c r="G12" s="49"/>
@@ -40036,19 +40033,19 @@
     </row>
     <row r="13" spans="1:22" ht="22.5" customHeight="1">
       <c r="A13" s="54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="131" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="131" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D13" s="131" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F13" s="35"/>
       <c r="G13" s="35"/>
@@ -40070,19 +40067,19 @@
     </row>
     <row r="14" spans="1:22" ht="22.5" customHeight="1">
       <c r="A14" s="41" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="55" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="55" t="s">
-        <v>120</v>
-      </c>
       <c r="D14" s="55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E14" s="42" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F14" s="42"/>
       <c r="G14" s="152">
@@ -40106,22 +40103,22 @@
     </row>
     <row r="15" spans="1:22" ht="22.5" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="C15" s="64" t="s">
+      <c r="D15" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="D15" s="14" t="s">
-        <v>215</v>
-      </c>
       <c r="E15" s="148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F15" s="144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G15" s="153">
         <v>27</v>
@@ -40144,22 +40141,22 @@
     </row>
     <row r="16" spans="1:22" ht="22.5" customHeight="1">
       <c r="A16" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" s="55" t="s">
         <v>226</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="D16" s="55" t="s">
         <v>227</v>
       </c>
-      <c r="D16" s="55" t="s">
-        <v>228</v>
-      </c>
       <c r="E16" s="143" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F16" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G16" s="152">
         <v>29</v>
@@ -40182,15 +40179,15 @@
     </row>
     <row r="17" spans="1:22" ht="22.5" customHeight="1">
       <c r="A17" s="33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="35"/>
       <c r="C17" s="64" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F17" s="35"/>
       <c r="G17" s="35"/>
@@ -40212,19 +40209,19 @@
     </row>
     <row r="18" spans="1:22" ht="22.5" customHeight="1">
       <c r="A18" s="56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C18" s="132" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="132" t="s">
         <v>200</v>
       </c>
-      <c r="D18" s="132" t="s">
-        <v>201</v>
-      </c>
       <c r="E18" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F18" s="42"/>
       <c r="G18" s="42"/>
@@ -40246,22 +40243,22 @@
     </row>
     <row r="19" spans="1:22" ht="22.5" customHeight="1">
       <c r="A19" s="44" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19" s="52" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="52" t="s">
         <v>238</v>
       </c>
-      <c r="C19" s="52" t="s">
+      <c r="D19" s="52" t="s">
         <v>239</v>
       </c>
-      <c r="D19" s="52" t="s">
-        <v>240</v>
-      </c>
       <c r="E19" s="89" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F19" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G19" s="87">
         <v>26</v>
@@ -40284,17 +40281,17 @@
     </row>
     <row r="20" spans="1:22" ht="22.5" customHeight="1">
       <c r="A20" s="56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="132" t="s">
+        <v>252</v>
+      </c>
+      <c r="C20" s="132" t="s">
         <v>253</v>
-      </c>
-      <c r="C20" s="132" t="s">
-        <v>254</v>
       </c>
       <c r="D20" s="142"/>
       <c r="E20" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F20" s="49"/>
       <c r="G20" s="49"/>
@@ -40316,19 +40313,19 @@
     </row>
     <row r="21" spans="1:22" ht="22.5" customHeight="1">
       <c r="A21" s="58" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B21" s="136" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C21" s="136" t="s">
+        <v>195</v>
+      </c>
+      <c r="D21" s="52" t="s">
         <v>196</v>
       </c>
-      <c r="D21" s="52" t="s">
-        <v>197</v>
-      </c>
       <c r="E21" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
@@ -40350,22 +40347,22 @@
     </row>
     <row r="22" spans="1:22" ht="22.5" customHeight="1">
       <c r="A22" s="57" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="129" t="s">
+        <v>222</v>
+      </c>
+      <c r="C22" s="129" t="s">
         <v>223</v>
       </c>
-      <c r="C22" s="129" t="s">
+      <c r="D22" s="129" t="s">
         <v>224</v>
       </c>
-      <c r="D22" s="129" t="s">
-        <v>225</v>
-      </c>
       <c r="E22" s="145" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F22" s="88" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G22" s="86">
         <v>29</v>
@@ -40388,19 +40385,19 @@
     </row>
     <row r="23" spans="1:22" ht="22.5" customHeight="1">
       <c r="A23" s="44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C23" s="52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E23" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F23" s="45"/>
       <c r="G23" s="45"/>
@@ -40422,19 +40419,19 @@
     </row>
     <row r="24" spans="1:22" ht="22.5" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D24" s="14" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E24" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F24" s="49"/>
       <c r="G24" s="49"/>
@@ -40456,19 +40453,19 @@
     </row>
     <row r="25" spans="1:22" ht="22.5" customHeight="1">
       <c r="A25" s="60" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" s="139" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="139" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D25" s="139" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
@@ -40490,19 +40487,19 @@
     </row>
     <row r="26" spans="1:22" ht="22.5" customHeight="1">
       <c r="A26" s="59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" s="137" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="137" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="137" t="s">
+      <c r="D26" s="137" t="s">
         <v>178</v>
       </c>
-      <c r="D26" s="137" t="s">
-        <v>179</v>
-      </c>
       <c r="E26" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F26" s="49"/>
       <c r="G26" s="49"/>
@@ -40524,22 +40521,22 @@
     </row>
     <row r="27" spans="1:22" ht="22.5" customHeight="1">
       <c r="A27" s="59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B27" s="137" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27" s="137" t="s">
         <v>229</v>
       </c>
-      <c r="C27" s="137" t="s">
+      <c r="D27" s="137" t="s">
         <v>230</v>
       </c>
-      <c r="D27" s="137" t="s">
-        <v>231</v>
-      </c>
       <c r="E27" s="148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F27" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G27" s="153">
         <v>24</v>
@@ -40562,15 +40559,15 @@
     </row>
     <row r="28" spans="1:22" ht="22.5" customHeight="1">
       <c r="A28" s="100" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" s="134"/>
       <c r="C28" s="133" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28" s="134"/>
       <c r="E28" s="43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F28" s="42"/>
       <c r="G28" s="42"/>
@@ -40592,17 +40589,17 @@
     </row>
     <row r="29" spans="1:22" ht="22.5" customHeight="1">
       <c r="A29" s="54" t="s">
+        <v>345</v>
+      </c>
+      <c r="B29" s="131" t="s">
         <v>346</v>
       </c>
-      <c r="B29" s="131" t="s">
+      <c r="C29" s="131" t="s">
         <v>347</v>
-      </c>
-      <c r="C29" s="131" t="s">
-        <v>348</v>
       </c>
       <c r="D29" s="141"/>
       <c r="E29" s="45" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F29" s="45"/>
       <c r="G29" s="45"/>
@@ -40624,20 +40621,20 @@
     </row>
     <row r="30" spans="1:22" ht="22.5" customHeight="1">
       <c r="A30" s="59" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B30" s="137" t="s">
+        <v>126</v>
+      </c>
+      <c r="C30" s="137" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="137" t="s">
+      <c r="D30" s="137" t="s">
         <v>128</v>
-      </c>
-      <c r="D30" s="137" t="s">
-        <v>129</v>
       </c>
       <c r="E30" s="148"/>
       <c r="F30" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G30" s="86">
         <v>12</v>
@@ -40660,22 +40657,22 @@
     </row>
     <row r="31" spans="1:22" ht="22.5" customHeight="1">
       <c r="A31" s="44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B31" s="52" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C31" s="52" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="52" t="s">
         <v>128</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="E31" s="89" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="89" t="s">
         <v>129</v>
-      </c>
-      <c r="E31" s="89" t="s">
-        <v>139</v>
-      </c>
-      <c r="F31" s="89" t="s">
-        <v>130</v>
       </c>
       <c r="G31" s="87">
         <v>13</v>
@@ -40698,19 +40695,19 @@
     </row>
     <row r="32" spans="1:22" ht="22.5" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B32" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="D32" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D32" s="14" t="s">
-        <v>118</v>
-      </c>
       <c r="E32" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F32" s="49"/>
       <c r="G32" s="86">
@@ -40734,13 +40731,13 @@
     </row>
     <row r="33" spans="1:22" ht="22.5" customHeight="1">
       <c r="A33" s="33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" s="64" t="s">
+        <v>146</v>
+      </c>
+      <c r="C33" s="64" t="s">
         <v>147</v>
-      </c>
-      <c r="C33" s="64" t="s">
-        <v>148</v>
       </c>
       <c r="D33" s="35"/>
       <c r="E33" s="35"/>
@@ -40764,17 +40761,17 @@
     </row>
     <row r="34" spans="1:22" ht="22.5" customHeight="1">
       <c r="A34" s="56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B34" s="132" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C34" s="132" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D34" s="142"/>
       <c r="E34" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -40796,22 +40793,22 @@
     </row>
     <row r="35" spans="1:22" ht="22.5" customHeight="1">
       <c r="A35" s="33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B35" s="64" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" s="64" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="64" t="s">
+      <c r="D35" s="64" t="s">
         <v>242</v>
       </c>
-      <c r="D35" s="64" t="s">
-        <v>243</v>
-      </c>
       <c r="E35" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F35" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G35" s="153">
         <v>27</v>
@@ -40834,20 +40831,20 @@
     </row>
     <row r="36" spans="1:22" ht="22.5" customHeight="1">
       <c r="A36" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B36" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" s="14" t="s">
         <v>248</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>249</v>
       </c>
       <c r="D36" s="49"/>
       <c r="E36" s="88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F36" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G36" s="86">
         <v>32</v>
@@ -40870,19 +40867,19 @@
     </row>
     <row r="37" spans="1:22" ht="22.5" customHeight="1">
       <c r="A37" s="44" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B37" s="52" t="s">
+        <v>261</v>
+      </c>
+      <c r="C37" s="52" t="s">
         <v>262</v>
       </c>
-      <c r="C37" s="52" t="s">
+      <c r="D37" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="D37" s="52" t="s">
-        <v>264</v>
-      </c>
       <c r="E37" s="45" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F37" s="45"/>
       <c r="G37" s="45"/>
@@ -40904,20 +40901,20 @@
     </row>
     <row r="38" spans="1:22" ht="22.5" customHeight="1">
       <c r="A38" s="41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B38" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="C38" s="55" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="55" t="s">
+      <c r="D38" s="55" t="s">
         <v>132</v>
-      </c>
-      <c r="D38" s="55" t="s">
-        <v>133</v>
       </c>
       <c r="E38" s="143"/>
       <c r="F38" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G38" s="152">
         <v>12</v>
@@ -40940,22 +40937,22 @@
     </row>
     <row r="39" spans="1:22" ht="22.5" customHeight="1">
       <c r="A39" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C39" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="64" t="s">
         <v>132</v>
       </c>
-      <c r="D39" s="64" t="s">
-        <v>133</v>
-      </c>
       <c r="E39" s="144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F39" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G39" s="153">
         <v>13</v>
@@ -40978,19 +40975,19 @@
     </row>
     <row r="40" spans="1:22" ht="22.5" customHeight="1">
       <c r="A40" s="100" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B40" s="133" t="s">
+        <v>249</v>
+      </c>
+      <c r="C40" s="133" t="s">
         <v>250</v>
       </c>
-      <c r="C40" s="133" t="s">
+      <c r="D40" s="133" t="s">
         <v>251</v>
       </c>
-      <c r="D40" s="133" t="s">
-        <v>252</v>
-      </c>
       <c r="E40" s="43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F40" s="42"/>
       <c r="G40" s="152">
@@ -41014,19 +41011,19 @@
     </row>
     <row r="41" spans="1:22" ht="22.5" customHeight="1">
       <c r="A41" s="61" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" s="140" t="s">
+        <v>258</v>
+      </c>
+      <c r="C41" s="140" t="s">
         <v>259</v>
       </c>
-      <c r="C41" s="140" t="s">
+      <c r="D41" s="140" t="s">
         <v>260</v>
       </c>
-      <c r="D41" s="140" t="s">
-        <v>261</v>
-      </c>
       <c r="E41" s="40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F41" s="35"/>
       <c r="G41" s="35"/>
@@ -41048,13 +41045,13 @@
     </row>
     <row r="42" spans="1:22" ht="22.5" customHeight="1">
       <c r="A42" s="127" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" s="32" t="s">
         <v>143</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>144</v>
       </c>
       <c r="D42" s="40"/>
       <c r="E42" s="40"/>
@@ -41078,13 +41075,13 @@
     </row>
     <row r="43" spans="1:22" ht="22.5" customHeight="1">
       <c r="A43" s="56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B43" s="132" t="s">
+        <v>189</v>
+      </c>
+      <c r="C43" s="132" t="s">
         <v>190</v>
-      </c>
-      <c r="C43" s="132" t="s">
-        <v>191</v>
       </c>
       <c r="D43" s="142"/>
       <c r="E43" s="49"/>
@@ -41108,19 +41105,19 @@
     </row>
     <row r="44" spans="1:22" ht="22.5" customHeight="1">
       <c r="A44" s="59" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B44" s="137" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C44" s="137" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" s="64" t="s">
         <v>198</v>
       </c>
-      <c r="D44" s="64" t="s">
-        <v>199</v>
-      </c>
       <c r="E44" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F44" s="35"/>
       <c r="G44" s="153">
@@ -41144,17 +41141,17 @@
     </row>
     <row r="45" spans="1:22" ht="22.5" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B45" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="C45" s="14" t="s">
         <v>256</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>257</v>
       </c>
       <c r="D45" s="49"/>
       <c r="E45" s="49" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F45" s="49"/>
       <c r="G45" s="49"/>
@@ -41176,22 +41173,22 @@
     </row>
     <row r="46" spans="1:22" ht="22.5" customHeight="1">
       <c r="A46" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C46" s="140" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D46" s="140" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E46" s="148" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F46" s="144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G46" s="153">
         <v>24</v>
@@ -41214,22 +41211,22 @@
     </row>
     <row r="47" spans="1:22" ht="22.5" customHeight="1">
       <c r="A47" s="57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B47" s="129" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="129" t="s">
         <v>220</v>
       </c>
-      <c r="C47" s="129" t="s">
+      <c r="D47" s="129" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="129" t="s">
-        <v>222</v>
-      </c>
       <c r="E47" s="151" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F47" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G47" s="152">
         <v>26</v>
@@ -41252,22 +41249,22 @@
     </row>
     <row r="48" spans="1:22" ht="22.5" customHeight="1">
       <c r="A48" s="58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B48" s="136" t="s">
+        <v>209</v>
+      </c>
+      <c r="C48" s="136" t="s">
         <v>210</v>
       </c>
-      <c r="C48" s="136" t="s">
+      <c r="D48" s="136" t="s">
         <v>211</v>
       </c>
-      <c r="D48" s="136" t="s">
-        <v>212</v>
-      </c>
       <c r="E48" s="150" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F48" s="89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G48" s="87">
         <v>30</v>
@@ -41290,13 +41287,13 @@
     </row>
     <row r="49" spans="1:22" ht="22.5" customHeight="1">
       <c r="A49" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B49" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" s="55" t="s">
         <v>145</v>
-      </c>
-      <c r="C49" s="55" t="s">
-        <v>146</v>
       </c>
       <c r="D49" s="49"/>
       <c r="E49" s="42"/>
@@ -41320,19 +41317,19 @@
     </row>
     <row r="50" spans="1:22" ht="22.5" customHeight="1">
       <c r="A50" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B50" s="64" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="64" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="64" t="s">
+      <c r="D50" s="64" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="64" t="s">
+      <c r="E50" s="35" t="s">
         <v>112</v>
-      </c>
-      <c r="E50" s="35" t="s">
-        <v>113</v>
       </c>
       <c r="F50" s="35"/>
       <c r="G50" s="35"/>
@@ -41354,20 +41351,20 @@
     </row>
     <row r="51" spans="1:22" ht="22.5" customHeight="1">
       <c r="A51" s="41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B51" s="55" t="s">
+        <v>157</v>
+      </c>
+      <c r="C51" s="55" t="s">
         <v>158</v>
       </c>
-      <c r="C51" s="55" t="s">
-        <v>159</v>
-      </c>
       <c r="D51" s="55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E51" s="143"/>
       <c r="F51" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G51" s="152">
         <v>11</v>
@@ -41393,20 +41390,20 @@
     </row>
     <row r="52" spans="1:22" ht="22.5" customHeight="1">
       <c r="A52" s="59" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B52" s="137" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C52" s="137" t="s">
+        <v>131</v>
+      </c>
+      <c r="D52" s="137" t="s">
         <v>132</v>
-      </c>
-      <c r="D52" s="137" t="s">
-        <v>133</v>
       </c>
       <c r="E52" s="148"/>
       <c r="F52" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G52" s="153">
         <v>11</v>
@@ -41432,26 +41429,26 @@
     </row>
     <row r="53" spans="1:22" ht="22.5" customHeight="1">
       <c r="A53" s="41" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D53" s="42"/>
       <c r="E53" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F53" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G53" s="42" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H53" s="156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I53" s="83"/>
       <c r="J53" s="83"/>
@@ -41470,16 +41467,16 @@
     </row>
     <row r="54" spans="1:22" ht="22.5" customHeight="1">
       <c r="A54" s="33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B54" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" s="64" t="s">
         <v>152</v>
       </c>
-      <c r="C54" s="64" t="s">
+      <c r="D54" s="64" t="s">
         <v>153</v>
-      </c>
-      <c r="D54" s="64" t="s">
-        <v>154</v>
       </c>
       <c r="E54" s="35"/>
       <c r="F54" s="35"/>
@@ -41502,16 +41499,16 @@
     </row>
     <row r="55" spans="1:22" ht="22.5" customHeight="1">
       <c r="A55" s="41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B55" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="C55" s="55" t="s">
+      <c r="D55" s="55" t="s">
         <v>150</v>
-      </c>
-      <c r="D55" s="55" t="s">
-        <v>151</v>
       </c>
       <c r="E55" s="42"/>
       <c r="F55" s="42"/>
@@ -41534,19 +41531,19 @@
     </row>
     <row r="56" spans="1:22" ht="22.5" customHeight="1">
       <c r="A56" s="60" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B56" s="139" t="s">
+        <v>113</v>
+      </c>
+      <c r="C56" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="C56" s="139" t="s">
-        <v>115</v>
-      </c>
       <c r="D56" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="E56" s="43" t="s">
         <v>112</v>
-      </c>
-      <c r="E56" s="43" t="s">
-        <v>113</v>
       </c>
       <c r="F56" s="45"/>
       <c r="G56" s="45"/>
@@ -41568,14 +41565,14 @@
     </row>
     <row r="57" spans="1:22" ht="22.5" customHeight="1">
       <c r="A57" s="60" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B57" s="130"/>
       <c r="C57" s="130"/>
       <c r="D57" s="130"/>
       <c r="E57" s="146"/>
       <c r="F57" s="143" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G57" s="42"/>
       <c r="H57" s="156"/>
@@ -41596,20 +41593,20 @@
     </row>
     <row r="58" spans="1:22" ht="22.5" customHeight="1">
       <c r="A58" s="58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B58" s="136" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="136" t="s">
         <v>169</v>
       </c>
-      <c r="C58" s="136" t="s">
-        <v>170</v>
-      </c>
       <c r="D58" s="136" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E58" s="150"/>
       <c r="F58" s="89" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G58" s="45"/>
       <c r="H58" s="85"/>
@@ -41630,20 +41627,20 @@
     </row>
     <row r="59" spans="1:22" ht="22.5" customHeight="1">
       <c r="A59" s="12" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C59" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D59" s="14" t="s">
         <v>132</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>133</v>
       </c>
       <c r="E59" s="88"/>
       <c r="F59" s="88" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G59" s="86">
         <v>12</v>
@@ -41666,20 +41663,20 @@
     </row>
     <row r="60" spans="1:22" ht="22.5" customHeight="1">
       <c r="A60" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B60" s="52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C60" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="D60" s="52" t="s">
         <v>132</v>
-      </c>
-      <c r="D60" s="52" t="s">
-        <v>133</v>
       </c>
       <c r="E60" s="89"/>
       <c r="F60" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G60" s="87">
         <v>13</v>
@@ -41702,20 +41699,20 @@
     </row>
     <row r="61" spans="1:22" ht="22.5" customHeight="1">
       <c r="A61" s="41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B61" s="55" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" s="55" t="s">
         <v>155</v>
       </c>
-      <c r="C61" s="55" t="s">
-        <v>156</v>
-      </c>
       <c r="D61" s="55" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E61" s="143"/>
       <c r="F61" s="143" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G61" s="152">
         <v>11</v>
@@ -41738,20 +41735,20 @@
     </row>
     <row r="62" spans="1:22" ht="22.5" customHeight="1">
       <c r="A62" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D62" s="64" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E62" s="144"/>
       <c r="F62" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G62" s="153">
         <v>11</v>
@@ -41774,20 +41771,20 @@
     </row>
     <row r="63" spans="1:22" ht="22.5" customHeight="1">
       <c r="A63" s="41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B63" s="55" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" s="55" t="s">
         <v>174</v>
       </c>
-      <c r="C63" s="55" t="s">
+      <c r="D63" s="55" t="s">
         <v>175</v>
-      </c>
-      <c r="D63" s="55" t="s">
-        <v>176</v>
       </c>
       <c r="E63" s="143"/>
       <c r="F63" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G63" s="42"/>
       <c r="H63" s="156"/>
@@ -41808,19 +41805,19 @@
     </row>
     <row r="64" spans="1:22" ht="22.5" customHeight="1">
       <c r="A64" s="44" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B64" s="52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" s="52" t="s">
         <v>123</v>
       </c>
-      <c r="C64" s="52" t="s">
+      <c r="D64" s="52" t="s">
         <v>124</v>
       </c>
-      <c r="D64" s="52" t="s">
+      <c r="E64" s="45" t="s">
         <v>125</v>
-      </c>
-      <c r="E64" s="45" t="s">
-        <v>126</v>
       </c>
       <c r="F64" s="45"/>
       <c r="G64" s="45"/>
@@ -41842,15 +41839,15 @@
     </row>
     <row r="65" spans="1:22" ht="22.5" customHeight="1">
       <c r="A65" s="41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B65" s="42"/>
       <c r="C65" s="55" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D65" s="42"/>
       <c r="E65" s="42" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F65" s="42"/>
       <c r="G65" s="42"/>
@@ -41872,16 +41869,16 @@
     </row>
     <row r="66" spans="1:22" ht="22.5" customHeight="1">
       <c r="A66" s="44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B66" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="52" t="s">
         <v>140</v>
       </c>
-      <c r="C66" s="52" t="s">
+      <c r="D66" s="52" t="s">
         <v>141</v>
-      </c>
-      <c r="D66" s="52" t="s">
-        <v>142</v>
       </c>
       <c r="E66" s="45"/>
       <c r="F66" s="45"/>
@@ -41906,20 +41903,20 @@
     </row>
     <row r="67" spans="1:22" ht="22.5" customHeight="1">
       <c r="A67" s="128" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B67" s="138" t="s">
+        <v>161</v>
+      </c>
+      <c r="C67" s="138" t="s">
         <v>162</v>
       </c>
-      <c r="C67" s="138" t="s">
+      <c r="D67" s="138" t="s">
         <v>163</v>
-      </c>
-      <c r="D67" s="138" t="s">
-        <v>164</v>
       </c>
       <c r="E67" s="90"/>
       <c r="F67" s="143" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G67" s="152">
         <v>20</v>
@@ -41942,20 +41939,20 @@
     </row>
     <row r="68" spans="1:22" ht="22.5" customHeight="1">
       <c r="A68" s="58" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B68" s="136" t="s">
+        <v>165</v>
+      </c>
+      <c r="C68" s="136" t="s">
         <v>166</v>
       </c>
-      <c r="C68" s="136" t="s">
+      <c r="D68" s="136" t="s">
         <v>167</v>
-      </c>
-      <c r="D68" s="136" t="s">
-        <v>168</v>
       </c>
       <c r="E68" s="149"/>
       <c r="F68" s="144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G68" s="153">
         <v>21</v>
@@ -41978,19 +41975,19 @@
     </row>
     <row r="69" spans="1:22" ht="22.5" customHeight="1">
       <c r="A69" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B69" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C69" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="C69" s="14" t="s">
-        <v>122</v>
-      </c>
       <c r="D69" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E69" s="49" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F69" s="49"/>
       <c r="G69" s="49"/>
@@ -42012,20 +42009,20 @@
     </row>
     <row r="70" spans="1:22" ht="22.5" customHeight="1">
       <c r="A70" s="58" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B70" s="136" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C70" s="136" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D70" s="136" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E70" s="149"/>
       <c r="F70" s="144" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G70" s="153">
         <v>9</v>
@@ -42048,19 +42045,19 @@
     </row>
     <row r="71" spans="1:22" ht="22.5" customHeight="1">
       <c r="A71" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B71" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C71" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="C71" s="14" t="s">
+      <c r="D71" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="E71" s="49" t="s">
         <v>204</v>
-      </c>
-      <c r="E71" s="49" t="s">
-        <v>205</v>
       </c>
       <c r="F71" s="49"/>
       <c r="G71" s="49"/>
@@ -42082,20 +42079,20 @@
     </row>
     <row r="72" spans="1:22" ht="22.5" customHeight="1">
       <c r="A72" s="41" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B72" s="52" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C72" s="52" t="s">
+        <v>131</v>
+      </c>
+      <c r="D72" s="52" t="s">
         <v>132</v>
-      </c>
-      <c r="D72" s="52" t="s">
-        <v>133</v>
       </c>
       <c r="E72" s="89"/>
       <c r="F72" s="89" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G72" s="87">
         <v>12</v>
@@ -42118,20 +42115,20 @@
     </row>
     <row r="73" spans="1:22" s="83" customFormat="1" ht="22.5" customHeight="1">
       <c r="A73" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B73" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C73" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D73" s="64" t="s">
         <v>132</v>
-      </c>
-      <c r="D73" s="64" t="s">
-        <v>133</v>
       </c>
       <c r="E73" s="144"/>
       <c r="F73" s="144" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G73" s="153">
         <v>13</v>
@@ -42140,20 +42137,20 @@
     </row>
     <row r="74" spans="1:22" s="83" customFormat="1" ht="22.5" customHeight="1">
       <c r="A74" s="125" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B74" s="135" t="s">
+        <v>215</v>
+      </c>
+      <c r="C74" s="135" t="s">
         <v>216</v>
       </c>
-      <c r="C74" s="135" t="s">
+      <c r="D74" s="53" t="s">
         <v>217</v>
-      </c>
-      <c r="D74" s="53" t="s">
-        <v>218</v>
       </c>
       <c r="E74" s="146"/>
       <c r="F74" s="146" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G74" s="155">
         <v>24</v>
@@ -42162,22 +42159,22 @@
     </row>
     <row r="75" spans="1:22" ht="22.5" customHeight="1">
       <c r="A75" s="44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B75" s="67" t="s">
+        <v>243</v>
+      </c>
+      <c r="C75" s="67" t="s">
         <v>244</v>
       </c>
-      <c r="C75" s="67" t="s">
+      <c r="D75" s="67" t="s">
         <v>245</v>
       </c>
-      <c r="D75" s="67" t="s">
+      <c r="E75" s="147" t="s">
         <v>246</v>
       </c>
-      <c r="E75" s="147" t="s">
-        <v>247</v>
-      </c>
       <c r="F75" s="147" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G75" s="154">
         <v>28</v>
@@ -64358,7 +64355,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:M35"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.54296875" customWidth="1"/>
     <col min="5" max="5" width="21.7265625" customWidth="1"/>
@@ -64366,24 +64363,24 @@
   <sheetData>
     <row r="1" spans="1:13" ht="22.5" customHeight="1">
       <c r="A1" s="91" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="106" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="109" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="106" t="s">
+      <c r="D1" s="105" t="s">
+        <v>308</v>
+      </c>
+      <c r="E1" s="91" t="s">
         <v>269</v>
-      </c>
-      <c r="C1" s="109" t="s">
-        <v>268</v>
-      </c>
-      <c r="D1" s="105" t="s">
-        <v>309</v>
-      </c>
-      <c r="E1" s="91" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="22.5" customHeight="1">
       <c r="A2" s="92" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B2" s="107">
         <v>5</v>
@@ -64396,12 +64393,12 @@
         <v>5</v>
       </c>
       <c r="E2" s="92" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="22.5" customHeight="1">
       <c r="A3" s="93" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B3" s="107">
         <v>1000</v>
@@ -64414,12 +64411,12 @@
         <v>1000</v>
       </c>
       <c r="E3" s="92" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="22.5" customHeight="1">
       <c r="A4" s="93" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B4" s="107">
         <v>1</v>
@@ -64432,7 +64429,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="103" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="22.5" customHeight="1">
@@ -64450,7 +64447,7 @@
         <v>10000</v>
       </c>
       <c r="E5" s="104" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="22.5" customHeight="1">
@@ -64468,7 +64465,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="104" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="22.5" customHeight="1">
@@ -64486,7 +64483,7 @@
         <v>5</v>
       </c>
       <c r="E7" s="104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G7" s="94"/>
       <c r="H7" s="94"/>
@@ -64511,7 +64508,7 @@
         <v>5</v>
       </c>
       <c r="E8" s="104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G8" s="94"/>
       <c r="H8" s="94"/>
@@ -64536,12 +64533,12 @@
         <v>5</v>
       </c>
       <c r="E9" s="104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="22.5" customHeight="1">
       <c r="A10" s="93" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B10" s="107">
         <v>5</v>
@@ -64554,12 +64551,12 @@
         <v>5</v>
       </c>
       <c r="E10" s="104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="22.5" customHeight="1">
       <c r="A11" s="93" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B11" s="107">
         <v>20</v>
@@ -64572,7 +64569,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="22.5" customHeight="1">
@@ -64592,7 +64589,7 @@
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1">
       <c r="A13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B13" s="107">
         <v>0.1</v>
@@ -64605,12 +64602,12 @@
         <v>0.1</v>
       </c>
       <c r="E13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1">
       <c r="A14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B14" s="107">
         <v>0.05</v>
@@ -64623,12 +64620,12 @@
         <v>0.05</v>
       </c>
       <c r="E14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1">
       <c r="A15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B15" s="107">
         <v>0.03</v>
@@ -64641,12 +64638,12 @@
         <v>0.03</v>
       </c>
       <c r="E15" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1">
       <c r="A16" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B16" s="107">
         <v>1.4999999999999999E-2</v>
@@ -64659,12 +64656,12 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="E16" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B17" s="107">
         <v>0</v>
@@ -64677,47 +64674,47 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B18" s="112"/>
       <c r="C18" s="113"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
       <c r="A19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B19" s="112"/>
       <c r="C19" s="113"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B20" s="112"/>
       <c r="C20" s="113"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
       <c r="A21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B21" s="112"/>
       <c r="C21" s="113"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
       <c r="A22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B22" s="112"/>
       <c r="C22" s="113"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
       <c r="A23" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B23" s="107">
         <v>0.1</v>
@@ -64730,12 +64727,12 @@
         <v>0.5</v>
       </c>
       <c r="E23" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1">
       <c r="A24" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B24" s="107">
         <v>0.08</v>
@@ -64748,12 +64745,12 @@
         <v>0.39999999999999997</v>
       </c>
       <c r="E24" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B25" s="107">
         <v>0.2</v>
@@ -64766,12 +64763,12 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
       <c r="A26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B26" s="107">
         <v>0.5</v>
@@ -64784,12 +64781,12 @@
         <v>2.5</v>
       </c>
       <c r="E26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
       <c r="A27" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B27" s="107">
         <v>0.15</v>
@@ -64802,12 +64799,12 @@
         <v>0.74999999999999989</v>
       </c>
       <c r="E27" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
       <c r="A28" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B28" s="122"/>
       <c r="C28" s="113">
@@ -64816,7 +64813,7 @@
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
       <c r="A29" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B29" s="107">
         <v>1</v>
@@ -64831,7 +64828,7 @@
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
       <c r="A30" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B30" s="107">
         <v>2</v>
@@ -64846,7 +64843,7 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
       <c r="A31" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B31" s="107">
         <v>2.5</v>
@@ -64861,7 +64858,7 @@
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B32" s="107">
         <v>3.3330000000000002</v>
@@ -64876,7 +64873,7 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B33" s="107">
         <v>4.5454499999999998</v>
@@ -64891,7 +64888,7 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B34" s="107">
         <v>6.66</v>
@@ -64927,7 +64924,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.54296875" customWidth="1"/>
     <col min="2" max="2" width="17.26953125" customWidth="1"/>
@@ -64937,54 +64934,54 @@
   <sheetData>
     <row r="1" spans="1:13" ht="44.25" customHeight="1">
       <c r="A1" s="91" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B1" s="91" t="s">
+        <v>276</v>
+      </c>
+      <c r="C1" s="95" t="s">
         <v>277</v>
       </c>
-      <c r="C1" s="95" t="s">
+      <c r="D1" s="96" t="s">
         <v>278</v>
       </c>
-      <c r="D1" s="96" t="s">
+      <c r="E1" s="96" t="s">
         <v>279</v>
       </c>
-      <c r="E1" s="96" t="s">
+      <c r="F1" s="96" t="s">
         <v>280</v>
       </c>
-      <c r="F1" s="96" t="s">
+      <c r="G1" s="96" t="s">
         <v>281</v>
       </c>
-      <c r="G1" s="96" t="s">
+      <c r="H1" s="96" t="s">
         <v>282</v>
       </c>
-      <c r="H1" s="96" t="s">
+      <c r="I1" s="96" t="s">
         <v>283</v>
       </c>
-      <c r="I1" s="96" t="s">
+      <c r="J1" s="96" t="s">
         <v>284</v>
       </c>
-      <c r="J1" s="96" t="s">
+      <c r="K1" s="96" t="s">
         <v>285</v>
       </c>
-      <c r="K1" s="96" t="s">
+      <c r="L1" s="96" t="s">
         <v>286</v>
       </c>
-      <c r="L1" s="96" t="s">
+      <c r="M1" s="96" t="s">
         <v>287</v>
-      </c>
-      <c r="M1" s="96" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="22.5" customHeight="1">
       <c r="A2" s="92" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B2" s="92">
         <v>9</v>
       </c>
       <c r="C2" s="92" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D2" s="92">
         <v>-45</v>
@@ -65025,7 +65022,7 @@
         <v>4</v>
       </c>
       <c r="C3" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D3" s="92">
         <v>4</v>
@@ -65066,7 +65063,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D4" s="92">
         <v>0</v>
@@ -65107,7 +65104,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D5" s="92">
         <v>0</v>
@@ -65148,7 +65145,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="97" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D6" s="103">
         <v>0</v>
@@ -65195,7 +65192,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="9" max="9" width="12.81640625" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" customWidth="1"/>
@@ -65205,40 +65202,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1">
       <c r="A1" s="91" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="105" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1" s="111" t="s">
+        <v>311</v>
+      </c>
+      <c r="D1" s="111" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1" s="111" t="s">
+        <v>313</v>
+      </c>
+      <c r="F1" s="111" t="s">
+        <v>314</v>
+      </c>
+      <c r="G1" s="111" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1" s="109" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="105" t="s">
-        <v>317</v>
-      </c>
-      <c r="C1" s="111" t="s">
-        <v>312</v>
-      </c>
-      <c r="D1" s="111" t="s">
-        <v>313</v>
-      </c>
-      <c r="E1" s="111" t="s">
-        <v>314</v>
-      </c>
-      <c r="F1" s="111" t="s">
-        <v>315</v>
-      </c>
-      <c r="G1" s="111" t="s">
-        <v>316</v>
-      </c>
-      <c r="H1" s="109" t="s">
+      <c r="I1" s="109" t="s">
         <v>293</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="J1" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="J1" s="109" t="s">
+      <c r="K1" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="109" t="s">
         <v>295</v>
-      </c>
-      <c r="K1" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="L1" s="109" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="22.5" customHeight="1">
@@ -65692,7 +65689,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:T11"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="9" max="9" width="12.81640625" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" customWidth="1"/>
@@ -65702,40 +65699,40 @@
   <sheetData>
     <row r="1" spans="1:20" ht="22.5" customHeight="1">
       <c r="A1" s="91" t="s">
+        <v>291</v>
+      </c>
+      <c r="B1" s="91" t="s">
+        <v>316</v>
+      </c>
+      <c r="C1" s="115" t="s">
+        <v>311</v>
+      </c>
+      <c r="D1" s="115" t="s">
+        <v>312</v>
+      </c>
+      <c r="E1" s="115" t="s">
+        <v>313</v>
+      </c>
+      <c r="F1" s="115" t="s">
+        <v>314</v>
+      </c>
+      <c r="G1" s="115" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1" s="109" t="s">
         <v>292</v>
       </c>
-      <c r="B1" s="91" t="s">
-        <v>317</v>
-      </c>
-      <c r="C1" s="115" t="s">
-        <v>312</v>
-      </c>
-      <c r="D1" s="115" t="s">
-        <v>313</v>
-      </c>
-      <c r="E1" s="115" t="s">
-        <v>314</v>
-      </c>
-      <c r="F1" s="115" t="s">
-        <v>315</v>
-      </c>
-      <c r="G1" s="115" t="s">
-        <v>316</v>
-      </c>
-      <c r="H1" s="109" t="s">
+      <c r="I1" s="109" t="s">
         <v>293</v>
       </c>
-      <c r="I1" s="109" t="s">
+      <c r="J1" s="109" t="s">
         <v>294</v>
       </c>
-      <c r="J1" s="109" t="s">
+      <c r="K1" s="109" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="109" t="s">
         <v>295</v>
-      </c>
-      <c r="K1" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="L1" s="109" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="22.5" customHeight="1">
@@ -66273,35 +66270,35 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="4" max="8" width="13.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="91" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B1" s="91" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C1" s="91" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D1" s="91" t="s">
+        <v>296</v>
+      </c>
+      <c r="E1" s="91" t="s">
         <v>297</v>
       </c>
-      <c r="E1" s="91" t="s">
+      <c r="F1" s="91" t="s">
         <v>298</v>
       </c>
-      <c r="F1" s="91" t="s">
+      <c r="G1" s="91" t="s">
         <v>299</v>
       </c>
-      <c r="G1" s="91" t="s">
+      <c r="H1" s="91" t="s">
         <v>300</v>
-      </c>
-      <c r="H1" s="91" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1">
@@ -66716,7 +66713,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="9" max="12" width="8.1796875" customWidth="1"/>
@@ -66725,40 +66722,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="22.5" customHeight="1">
       <c r="A1" s="91" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B1" s="106" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C1" s="106" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D1" s="109" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E1" s="106" t="s">
+        <v>324</v>
+      </c>
+      <c r="F1" s="106" t="s">
         <v>325</v>
       </c>
-      <c r="F1" s="106" t="s">
+      <c r="G1" s="106" t="s">
         <v>326</v>
       </c>
-      <c r="G1" s="106" t="s">
+      <c r="H1" s="106" t="s">
         <v>327</v>
       </c>
-      <c r="H1" s="106" t="s">
-        <v>328</v>
-      </c>
       <c r="I1" s="109" t="s">
+        <v>301</v>
+      </c>
+      <c r="J1" s="109" t="s">
         <v>302</v>
       </c>
-      <c r="J1" s="109" t="s">
+      <c r="K1" s="109" t="s">
         <v>303</v>
       </c>
-      <c r="K1" s="109" t="s">
+      <c r="L1" s="109" t="s">
         <v>304</v>
-      </c>
-      <c r="L1" s="109" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="22.5" customHeight="1">

--- a/Versionen/brettspiel-sept-final/game_data.xlsx
+++ b/Versionen/brettspiel-sept-final/game_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schneids\code\KlimSta-Brettspiel\Versionen\brettspiel-sept-final\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\_Privat\Coding\KlimSta\Versionen\brettspiel-sept-final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639654F2-8CF8-4295-8415-EE4B69F6CA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AC8467E-6180-439E-BB6F-A57751201A4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="873" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Massnahmenkarten Spielwerte" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,9 @@
   <commentList>
     <comment ref="C1" authorId="0" shapeId="0" xr:uid="{884F3275-8B47-4A24-9A63-26455AFB7D59}">
       <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     KgCO2/m²a</t>
       </text>
     </comment>
@@ -92,18 +92,18 @@
   <commentList>
     <comment ref="C2" authorId="0" shapeId="0" xr:uid="{EF592111-A8C2-4853-9B03-5FD652A65E13}">
       <text>
-        <t xml:space="preserve">[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     €/m²
 </t>
       </text>
     </comment>
     <comment ref="H2" authorId="1" shapeId="0" xr:uid="{42E090DF-C6E0-4ACF-94D0-539FD66BF793}">
       <text>
-        <t>[Kommentarthread]
-Ihre Version von Excel gestattet Ihnen das Lesen dieses Kommentarthreads. Jegliche Bearbeitungen daran werden jedoch entfernt, wenn die Datei in einer neueren Version von Excel geöffnet wird. Weitere Informationen: https://go.microsoft.com/fwlink/?linkid=870924.
-Kommentar:
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
     Geld token</t>
       </text>
     </comment>
@@ -1851,9 +1851,6 @@
     <t>Private Ladestationen</t>
   </si>
   <si>
-    <t>Ladepunkte machen das Gebäude attraktiver für Nutzer:innen mit E-Autos. Sie steigern den Strombedarf, können aber auch als flexible Speichermöglichkeit genutzt werden (in Kombination mit Bi-Direktionalem Laden")."</t>
-  </si>
-  <si>
     <t>"Voraussetzung: Keine Fassadenbegrünung"</t>
   </si>
   <si>
@@ -1879,6 +1876,9 @@
   </si>
   <si>
     <t>"Eine Grundwasser-Wärmepumpe nutzt die relativ konstante Temperatur des Grundwassers und kann sehr effizient heizen und kühlen. Sie spart viele Emissionen, ist aber teuer, genehmigungspflichtig und nur bei geeigneten StandortVoraussetzungen möglich."</t>
+  </si>
+  <si>
+    <t>"Ladepunkte machen das Gebäude attraktiver für Nutzer:innen mit E-Autos. Sie steigern den Strombedarf, können aber auch als flexible Speichermöglichkeit genutzt werden (in Kombination mit Bi-Direktionalem Laden)."</t>
   </si>
 </sst>
 </file>
@@ -3080,7 +3080,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="87">
     <dxf>
@@ -4769,7 +4769,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AJ1002"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.54296875" customWidth="1"/>
     <col min="3" max="3" width="5.1796875" customWidth="1"/>
@@ -5164,7 +5164,7 @@
       <c r="U5" s="21"/>
       <c r="V5" s="39"/>
       <c r="W5" s="126" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="X5" s="53" t="s">
         <v>0</v>
@@ -5320,7 +5320,7 @@
         <v>1</v>
       </c>
       <c r="W7" s="82" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="X7" s="53" t="s">
         <v>3</v>
@@ -5477,7 +5477,7 @@
       <c r="U9" s="21"/>
       <c r="V9" s="39"/>
       <c r="W9" s="82" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="X9" s="32"/>
       <c r="Y9" s="32"/>
@@ -5625,7 +5625,7 @@
       <c r="U11" s="21"/>
       <c r="V11" s="39"/>
       <c r="W11" s="126" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="X11" s="56"/>
       <c r="Y11" s="40"/>
@@ -5700,7 +5700,7 @@
       <c r="U12" s="21"/>
       <c r="V12" s="39"/>
       <c r="W12" s="126" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="X12" s="43" t="s">
         <v>0</v>
@@ -5777,7 +5777,7 @@
       <c r="U13" s="21"/>
       <c r="V13" s="39"/>
       <c r="W13" s="126" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="X13" s="102" t="s">
         <v>0</v>
@@ -5854,7 +5854,7 @@
       <c r="U14" s="21"/>
       <c r="V14" s="39"/>
       <c r="W14" s="82" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="X14" s="53" t="s">
         <v>3</v>
@@ -6156,7 +6156,7 @@
       <c r="U18" s="21"/>
       <c r="V18" s="39"/>
       <c r="W18" s="126" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="X18" s="32" t="s">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>-3EN&amp;nbsp;+2BM&amp;nbsp;+3FL&amp;nbsp;+1ZU</v>
       </c>
       <c r="AB22" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="AC22" s="42" t="s">
         <v>526</v>
@@ -6565,7 +6565,7 @@
         <v>2</v>
       </c>
       <c r="W23" s="82" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="X23" s="53" t="s">
         <v>10</v>
@@ -6650,7 +6650,7 @@
         <v>2</v>
       </c>
       <c r="W24" s="82" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="X24" s="32" t="s">
         <v>10</v>
@@ -6733,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="W25" s="82" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="X25" s="32" t="s">
         <v>10</v>
@@ -6816,7 +6816,7 @@
         <v>2</v>
       </c>
       <c r="W26" s="82" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="X26" s="53" t="s">
         <v>10</v>
@@ -6897,7 +6897,7 @@
         <v>2</v>
       </c>
       <c r="W27" s="82" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="X27" s="53" t="s">
         <v>10</v>
@@ -10394,7 +10394,7 @@
         <v>+2EF&amp;nbsp;WP</v>
       </c>
       <c r="AB71" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AC71" s="64" t="s">
         <v>570</v>
@@ -39603,7 +39603,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:V996"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33.453125" customWidth="1"/>
     <col min="2" max="4" width="35.1796875" customWidth="1"/>
@@ -64355,7 +64355,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.54296875" customWidth="1"/>
     <col min="5" max="5" width="21.7265625" customWidth="1"/>
@@ -64924,7 +64924,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:M6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="17.54296875" customWidth="1"/>
     <col min="2" max="2" width="17.26953125" customWidth="1"/>
@@ -65192,7 +65192,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="9" max="9" width="12.81640625" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" customWidth="1"/>
@@ -65689,7 +65689,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:T11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="9" max="9" width="12.81640625" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" customWidth="1"/>
@@ -66270,7 +66270,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="4" max="8" width="13.1796875" customWidth="1"/>
   </cols>
@@ -66713,7 +66713,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.7265625" customWidth="1"/>
     <col min="9" max="12" width="8.1796875" customWidth="1"/>
